--- a/lessons/chess/excels/remarks_lcs_star.xlsx
+++ b/lessons/chess/excels/remarks_lcs_star.xlsx
@@ -162,7 +162,7 @@
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>+;* (12:35:18.198), -border (12:35:31.651), -document (12:37:53.239), -border (12:45:17.066), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00), +documnet (00:00:00), +broder (00:00:00), +selectedpiece (00:00:00), +replace (00:00:00), +Children (00:00:00), +selectedpisce (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +broder (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +broder (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00)</t>
+        <t>+;* (12:35:18.198), -border (12:35:31.651) ~0.67, -document (12:37:53.239) ~0.75, -border (12:45:17.066) ~0.67, -selectedPiece (12:51:24.571) ~0.92, -selectedPiece (12:52:11.048) ~0.92, -replaceChildren (12:52:19.891) ~0.47, -selectedPiece (12:52:27.102) ~0.85, -selectedPiece (12:52:30.641) ~0.92, -selectedPiece (12:53:29.626) ~0.92, +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00), +documnet (00:00:00), +broder (00:00:00), +selectedpiece (00:00:00), +replace (00:00:00), +Children (00:00:00), +selectedpisce (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +broder (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +broder (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -182,12 +182,12 @@
     </comment>
     <comment ref="M5" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (11:53:34.288), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +DOCTYOE (00:00:00), +handleclick (00:00:00)</t>
+        <t>-DOCTYPE (11:53:34.288) ~0.86, +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +DOCTYOE (00:00:00), +handleclick (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q5" authorId="0" shapeId="0">
       <text>
-        <t>-handleClick (12:33:15.189), -} (12:33:32.526), -handleClick (12:41:05.134), -selectedPiece (12:51:24.571), +const* (12:56:52.436), -let (12:56:53.102), +selectedpPiece (00:00:00), +handleclick (00:00:00), +hanleclick (00:00:00)</t>
+        <t>-handleClick (12:33:15.189) ~0.82, -} (12:33:32.526), -handleClick (12:41:05.134) ~0.91, -selectedPiece (12:51:24.571) ~0.93, +const* (12:56:52.436), -let (12:56:53.102), +selectedpPiece (00:00:00), +handleclick (00:00:00), +hanleclick (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
@@ -207,17 +207,17 @@
     </comment>
     <comment ref="M9" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (11:57:53.359), -&lt; (11:58:31.329), -/ (11:58:31.581), -div (11:58:32.273), -&gt; (11:58:32.462), -&lt; (11:58:34.148), -div (11:58:34.737), -class (11:58:35.647), -= (11:58:35.832), -" (11:58:35.965), -cell (11:58:36.694), -dark (11:58:37.525), -" (11:58:37.701), -&gt; (11:58:37.856), -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -&gt; (12:08:20.903), -&lt; (12:08:20.913), -/ (12:08:20.923), -div (12:08:20.953), -&gt; (12:08:20.963), -&lt; (12:08:20.983), -div (12:08:21.013), -class (12:08:21.073), -= (12:08:21.083), -" (12:08:21.093), -cell (12:08:21.133), -dark (12:08:21.183), -" (12:08:21.193), -&gt; (12:08:21.203), -&lt; (12:08:21.213), -/ (12:08:21.223), -div (12:08:21.253), -&gt; (12:08:21.263), -&lt; (12:08:21.283), -div (12:08:21.313), -class (12:08:21.373), -= (12:08:21.383), -" (12:08:21.393), -cell (12:08:21.433), -light (12:08:21.493), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -" (12:08:22.413), -div (12:08:24.673), -class (12:08:24.733), -= (12:08:24.743), -" (12:08:24.753), -cell (12:08:24.793), -light (12:08:24.853), -" (12:08:24.863), -&gt; (12:08:24.873), -&lt; (12:08:24.883), -/ (12:08:24.893), -div (12:08:24.923), -&gt; (12:08:24.933), -&lt; (12:08:24.963), -div (12:08:24.993), -class (12:08:25.053), -= (12:08:25.063), -" (12:08:25.073), -cell (12:08:25.113), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -dark (12:08:25.473), -" (12:08:25.483), -&gt; (12:08:25.493), -&lt; (12:08:25.503), -/ (12:08:25.513), -div (12:08:25.543), -&gt; (12:08:25.553), -&lt; (12:08:25.573), -div (12:08:25.603), -class (12:08:25.663), -= (12:08:25.673), -" (12:08:25.683), -cell (12:08:25.723), -light (12:08:25.783), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -" (12:08:27.313), -&gt; (12:08:27.323), -&lt; (12:08:27.333), -/ (12:08:27.343), -div (12:08:27.373), -&gt; (12:08:27.383), -&lt; (12:08:27.413), -div (12:08:27.443), -class (12:08:27.503), -= (12:08:27.513), -" (12:08:27.523), -cell (12:08:27.563), -dark (12:08:27.613), -" (12:08:27.623), -&gt; (12:08:27.633), -&lt; (12:08:27.643), -/ (12:08:27.653), -div (12:08:27.683), -&gt; (12:08:27.693), -&lt; (12:08:27.713), -div (12:08:27.743), -class (12:08:27.803), -= (12:08:27.813), -" (12:08:27.823), -cell (12:08:27.863), -light (12:08:27.923), -" (12:08:27.933), -&gt; (12:08:27.943), -&lt; (12:08:27.953), -/ (12:08:27.963), -div (12:08:27.993), -&gt; (12:08:28.003), -&lt; (12:08:28.023), -div (12:08:28.053), -class (12:08:28.113), -= (12:08:28.123), -" (12:08:28.133), -cell (12:08:28.173), -dark (12:08:28.223), -" (12:08:28.233), -&gt; (12:08:28.243), -&lt; (12:08:28.253), -/ (12:08:28.263), -div (12:08:28.293), -&gt; (12:08:28.303), -&lt; (12:08:28.323), -div (12:08:28.353), -class (12:08:28.413), -= (12:08:28.423), -" (12:08:28.433), -cell (12:08:28.473), -light (12:08:28.533), -" (12:08:28.543), -&gt; (12:08:28.553), -&lt; (12:08:28.563), -/ (12:08:28.573), -div (12:08:28.603), -&gt; (12:08:28.613), -&lt; (12:08:28.633), -div (12:08:28.663), -class (12:08:28.723), -= (12:08:28.733), -" (12:08:28.743), -cell (12:08:28.783), -dark (12:08:28.833), -" (12:08:28.843), -&gt; (12:08:28.853), -&lt; (12:08:28.863), -/ (12:08:28.873), -div (12:08:28.903), -&gt; (12:08:28.913), -&lt; (12:08:28.933), -div (12:08:28.963), -class (12:08:29.023), -= (12:08:29.033), -" (12:08:29.043), -cell (12:08:29.083), -light (12:08:29.143), -" (12:08:29.153), -&gt; (12:08:29.163), -&lt; (12:08:29.173), -/ (12:08:29.183), -div (12:08:29.213), -&gt; (12:08:29.223), -&lt; (12:08:29.243), -div (12:08:29.273), -class (12:08:29.333), -= (12:08:29.343), -" (12:08:29.353), -cell (12:08:29.393), -dark (12:08:29.443), -" (12:08:29.453), -&gt; (12:08:29.463), -&lt; (12:08:29.473), -/ (12:08:29.483), -div (12:08:29.513), -&gt; (12:08:29.523), -&lt; (12:08:29.543), -div (12:08:29.573), -class (12:08:29.633), -= (12:08:29.643), -" (12:08:29.653), -cell (12:08:29.693), -light (12:08:29.753), -" (12:08:29.763), -&gt; (12:08:29.773), -&lt; (12:08:29.783), -/ (12:08:29.793), -div (12:08:29.823), -&gt; (12:08:29.833), -&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -/ (12:16:05.559), -p2 (12:16:05.801), -&gt; (12:16:07.243), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +c (00:00:00), +: (00:00:00), +\ (00:00:00), +\ (00:00:00), +pieces (00:00:00), +\ (00:00:00), +rook (00:00:00), +. (00:00:00), +png (00:00:00)</t>
+        <t>-&lt; (11:57:53.359), -&lt; (11:58:31.329), -/ (11:58:31.581), -div (11:58:32.273), -&gt; (11:58:32.462), -&lt; (11:58:34.148), -div (11:58:34.737), -class (11:58:35.647), -= (11:58:35.832), -" (11:58:35.965), -cell (11:58:36.694), -dark (11:58:37.525), -" (11:58:37.701), -&gt; (11:58:37.856), -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -&gt; (12:08:20.903), -&lt; (12:08:20.913), -/ (12:08:20.923), -div (12:08:20.953), -&gt; (12:08:20.963), -&lt; (12:08:20.983), -div (12:08:21.013), -class (12:08:21.073), -= (12:08:21.083), -" (12:08:21.093), -cell (12:08:21.133), -dark (12:08:21.183), -" (12:08:21.193), -&gt; (12:08:21.203), -&lt; (12:08:21.213), -/ (12:08:21.223), -div (12:08:21.253), -&gt; (12:08:21.263), -&lt; (12:08:21.283), -div (12:08:21.313), -class (12:08:21.373), -= (12:08:21.383), -" (12:08:21.393), -cell (12:08:21.433), -light (12:08:21.493), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -" (12:08:22.413), -div (12:08:24.673), -class (12:08:24.733), -= (12:08:24.743), -" (12:08:24.753), -cell (12:08:24.793), -light (12:08:24.853), -" (12:08:24.863), -&gt; (12:08:24.873), -&lt; (12:08:24.883), -/ (12:08:24.893), -div (12:08:24.923), -&gt; (12:08:24.933), -&lt; (12:08:24.963), -div (12:08:24.993), -class (12:08:25.053), -= (12:08:25.063), -" (12:08:25.073), -cell (12:08:25.113), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -dark (12:08:25.473), -" (12:08:25.483), -&gt; (12:08:25.493), -&lt; (12:08:25.503), -/ (12:08:25.513), -div (12:08:25.543), -&gt; (12:08:25.553), -&lt; (12:08:25.573), -div (12:08:25.603), -class (12:08:25.663), -= (12:08:25.673), -" (12:08:25.683), -cell (12:08:25.723), -light (12:08:25.783), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -" (12:08:27.313), -&gt; (12:08:27.323), -&lt; (12:08:27.333), -/ (12:08:27.343), -div (12:08:27.373), -&gt; (12:08:27.383), -&lt; (12:08:27.413), -div (12:08:27.443), -class (12:08:27.503), -= (12:08:27.513), -" (12:08:27.523), -cell (12:08:27.563), -dark (12:08:27.613), -" (12:08:27.623), -&gt; (12:08:27.633), -&lt; (12:08:27.643), -/ (12:08:27.653), -div (12:08:27.683), -&gt; (12:08:27.693), -&lt; (12:08:27.713), -div (12:08:27.743), -class (12:08:27.803), -= (12:08:27.813), -" (12:08:27.823), -cell (12:08:27.863), -light (12:08:27.923), -" (12:08:27.933), -&gt; (12:08:27.943), -&lt; (12:08:27.953), -/ (12:08:27.963), -div (12:08:27.993), -&gt; (12:08:28.003), -&lt; (12:08:28.023), -div (12:08:28.053), -class (12:08:28.113), -= (12:08:28.123), -" (12:08:28.133), -cell (12:08:28.173), -dark (12:08:28.223), -" (12:08:28.233), -&gt; (12:08:28.243), -&lt; (12:08:28.253), -/ (12:08:28.263), -div (12:08:28.293), -&gt; (12:08:28.303), -&lt; (12:08:28.323), -div (12:08:28.353), -class (12:08:28.413), -= (12:08:28.423), -" (12:08:28.433), -cell (12:08:28.473), -light (12:08:28.533), -" (12:08:28.543), -&gt; (12:08:28.553), -&lt; (12:08:28.563), -/ (12:08:28.573), -div (12:08:28.603), -&gt; (12:08:28.613), -&lt; (12:08:28.633), -div (12:08:28.663), -class (12:08:28.723), -= (12:08:28.733), -" (12:08:28.743), -cell (12:08:28.783), -dark (12:08:28.833), -" (12:08:28.843), -&gt; (12:08:28.853), -&lt; (12:08:28.863), -/ (12:08:28.873), -div (12:08:28.903), -&gt; (12:08:28.913), -&lt; (12:08:28.933), -div (12:08:28.963), -class (12:08:29.023), -= (12:08:29.033), -" (12:08:29.043), -cell (12:08:29.083), -light (12:08:29.143), -" (12:08:29.153), -&gt; (12:08:29.163), -&lt; (12:08:29.173), -/ (12:08:29.183), -div (12:08:29.213), -&gt; (12:08:29.223), -&lt; (12:08:29.243), -div (12:08:29.273), -class (12:08:29.333), -= (12:08:29.343), -" (12:08:29.353), -cell (12:08:29.393), -dark (12:08:29.443), -" (12:08:29.453), -&gt; (12:08:29.463), -&lt; (12:08:29.473), -/ (12:08:29.483), -div (12:08:29.513), -&gt; (12:08:29.523), -&lt; (12:08:29.543), -div (12:08:29.573), -class (12:08:29.633), -= (12:08:29.643), -" (12:08:29.653), -cell (12:08:29.693), -light (12:08:29.753), -" (12:08:29.763), -&gt; (12:08:29.773), -&lt; (12:08:29.783), -/ (12:08:29.793), -div (12:08:29.823), -&gt; (12:08:29.833), -&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -/ (12:16:05.559), -p2 (12:16:05.801) ~0.33, -&gt; (12:16:07.243), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +c (00:00:00), +: (00:00:00), +\ (00:00:00), +\ (00:00:00), +pieces (00:00:00), +\ (00:00:00), +rook (00:00:00), +. (00:00:00), +png (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O9" authorId="0" shapeId="0">
       <text>
-        <t>-width (12:03:53.681), -: (12:03:53.818), -400px (12:03:55.740), -; (12:03:56.458), -height (12:03:58.438), -: (12:03:58.649), -400px (12:03:59.637), -; (12:03:59.993), -1fr (12:04:39.902), -1fr (12:05:20.402), -} (12:17:44.771), -50 (12:20:14.705), -display (12:24:00.258), -flex (12:24:01.038), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621), -( (12:27:04.730), -) (12:27:05.426), +width (00:00:00), +50px (00:00:00), +height (00:00:00), +50px (00:00:00), +50px (00:00:00), +50px (00:00:00), +100 (00:00:00), +height (00:00:00)</t>
+        <t>-width (12:03:53.681), -: (12:03:53.818), -400px (12:03:55.740), -; (12:03:56.458), -height (12:03:58.438), -: (12:03:58.649), -400px (12:03:59.637), -; (12:03:59.993), -1fr (12:04:39.902) ~0.00, -1fr (12:05:20.402) ~0.00, -} (12:17:44.771), -50 (12:20:14.705) ~0.33, -display (12:24:00.258) ~0.14, -flex (12:24:01.038) ~0.25, -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000) ~0.00, -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621) ~0.17, -( (12:27:04.730), -) (12:27:05.426), +width (00:00:00), +50px (00:00:00), +height (00:00:00), +50px (00:00:00), +50px (00:00:00), +50px (00:00:00), +100 (00:00:00), +height (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q9" authorId="0" shapeId="0">
       <text>
-        <t>-} (12:33:32.526), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102), +) (00:00:00), +; (00:00:00), +let (00:00:00), +selectedPiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +const (00:00:00), +cells (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +cell (00:00:00), +" (00:00:00), +if (00:00:00), +( (00:00:00), +selectedPiece (00:00:00), +! (00:00:00), += (00:00:00), +null (00:00:00), +) (00:00:00), +{ (00:00:00), +element (00:00:00), +. (00:00:00), +replaceChildren (00:00:00), +( (00:00:00), +selectdPiece (00:00:00), +) (00:00:00), +; (00:00:00), +selectedPiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +if (00:00:00), +( (00:00:00), +element (00:00:00), +. (00:00:00), +children (00:00:00), +. (00:00:00), +length (00:00:00), +&gt; (00:00:00), +0 (00:00:00), +) (00:00:00), +{ (00:00:00), +selectedPeiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-} (12:33:32.526), -selectedPiece (12:51:24.571) ~1.00, -= (12:51:25.051) ~1.00, -null (12:51:25.997) ~1.00, -; (12:51:26.172) ~1.00, -if (12:52:09.187) ~1.00, -( (12:52:09.526) ~1.00, -selectedPiece (12:52:11.048) ~1.00, -! (12:52:11.221) ~1.00, -= (12:52:11.422) ~1.00, -null (12:52:12.167) ~1.00, -) (12:52:12.282) ~1.00, -{ (12:52:13.202) ~1.00, -} (12:52:13.907) ~1.00, -element (12:52:17.350) ~1.00, -. (12:52:17.520) ~1.00, -replaceChildren (12:52:19.891) ~1.00, -( (12:52:20.134) ~1.00, -selectedPiece (12:52:27.102) ~0.92, -) (12:52:27.322) ~1.00, -; (12:52:27.519) ~1.00, -selectedPiece (12:52:30.641) ~1.00, -= (12:52:30.798) ~1.00, -null (12:52:31.700) ~1.00, -; (12:52:31.752) ~1.00, -else (12:53:21.083) ~1.00, -if (12:53:21.591) ~1.00, -( (12:53:21.914) ~1.00, -element (12:53:22.881) ~1.00, -. (12:53:23.171) ~1.00, -children (12:53:24.251) ~1.00, -. (12:53:24.441) ~1.00, -length (12:53:25.380) ~1.00, -&gt; (12:53:25.564) ~1.00, -0 (12:53:25.976) ~1.00, -) (12:53:26.161) ~1.00, -{ (12:53:26.816) ~1.00, -selectedPiece (12:53:29.626) ~0.93, -= (12:53:29.829) ~1.00, -element (12:53:30.892) ~1.00, -. (12:53:31.019) ~1.00, -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598) ~0.00, -; (12:53:33.056) ~1.00, -let (12:56:53.102) ~1.00, +) (00:00:00), +; (00:00:00), +let (00:00:00), +selectedPiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +const (00:00:00), +cells (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +cell (00:00:00), +" (00:00:00), +if (00:00:00), +( (00:00:00), +selectedPiece (00:00:00), +! (00:00:00), += (00:00:00), +null (00:00:00), +) (00:00:00), +{ (00:00:00), +element (00:00:00), +. (00:00:00), +replaceChildren (00:00:00), +( (00:00:00), +selectdPiece (00:00:00), +) (00:00:00), +; (00:00:00), +selectedPiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +if (00:00:00), +( (00:00:00), +element (00:00:00), +. (00:00:00), +children (00:00:00), +. (00:00:00), +length (00:00:00), +&gt; (00:00:00), +0 (00:00:00), +) (00:00:00), +{ (00:00:00), +selectedPeiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E12" authorId="0" shapeId="0">
@@ -252,12 +252,12 @@
     </comment>
     <comment ref="M19" authorId="0" shapeId="0">
       <text>
-        <t>-" (12:25:37.915), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +class (00:00:00), += (00:00:00), +" (00:00:00), +invert (00:00:00), +- (00:00:00), +color (00:00:00), +" (00:00:00)</t>
+        <t>-" (12:25:37.915) ~1.00, -class (12:26:40.137) ~1.00, -= (12:26:40.349) ~1.00, -" (12:26:40.406), -invert (12:26:41.264) ~1.00, -- (12:26:41.305) ~1.00, -color (12:26:42.154) ~1.00, +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +class (00:00:00), += (00:00:00), +" (00:00:00), +invert (00:00:00), +- (00:00:00), +color (00:00:00), +" (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q19" authorId="0" shapeId="0">
       <text>
-        <t>-border (12:35:31.651), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -let (12:56:53.102), +boder (00:00:00)</t>
+        <t>-border (12:35:31.651) ~0.83, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -let (12:56:53.102), +boder (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E21" authorId="0" shapeId="0">
@@ -277,12 +277,12 @@
     </comment>
     <comment ref="M21" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (11:53:34.288), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Doctype (00:00:00), +" (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00)</t>
+        <t>-DOCTYPE (11:53:34.288) ~0.14, +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Doctype (00:00:00), +" (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O21" authorId="0" shapeId="0">
       <text>
-        <t>-gray (12:02:56.667), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +grey (00:00:00)</t>
+        <t>-gray (12:02:56.667) ~0.75, -: (12:24:02.925) ~1.00, -center (12:24:03.906) ~1.00, -; (12:24:04.138) ~1.00, -justify (12:24:05.215) ~1.00, -- (12:24:05.313) ~1.00, -content (12:24:06.156) ~1.00, +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +grey (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q21" authorId="0" shapeId="0">
@@ -332,17 +332,17 @@
     </comment>
     <comment ref="M25" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (11:53:34.288), -Chess (11:54:35.668), -/ (12:16:06.943), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Doctype (00:00:00), +chess (00:00:00), +handleclick (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00)</t>
+        <t>-DOCTYPE (11:53:34.288) ~0.14, -Chess (11:54:35.668) ~0.80, -/ (12:16:06.943) ~1.00, +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Doctype (00:00:00), +chess (00:00:00), +handleclick (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
-        <t>-gray (12:02:56.667), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), +grey (00:00:00)</t>
+        <t>-gray (12:02:56.667) ~0.75, -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), +grey (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q25" authorId="0" shapeId="0">
       <text>
-        <t>-handleClick (12:33:15.189), -handleClick (12:41:05.134), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -length (12:53:25.380), -selectedPiece (12:53:29.626), +const* (12:56:52.436), -let (12:56:53.102), +selectedpice (00:00:00), +handleclick (00:00:00), +handleclick (00:00:00), +selectedpiece (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +lenght (00:00:00), +selectedpiece (00:00:00)</t>
+        <t>-handleClick (12:33:15.189) ~0.91, -handleClick (12:41:05.134) ~0.91, -selectedPiece (12:51:24.571) ~0.85, -selectedPiece (12:52:11.048) ~0.92, -replaceChildren (12:52:19.891) ~0.93, -selectedPiece (12:52:27.102) ~0.92, -selectedPiece (12:52:30.641) ~0.92, -length (12:53:25.380) ~0.67, -selectedPiece (12:53:29.626) ~0.92, +const* (12:56:52.436), -let (12:56:53.102), +selectedpice (00:00:00), +handleclick (00:00:00), +handleclick (00:00:00), +selectedpiece (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +lenght (00:00:00), +selectedpiece (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
@@ -362,7 +362,7 @@
     </comment>
     <comment ref="O30" authorId="0" shapeId="0">
       <text>
-        <t>-display (12:04:30.837), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), +dispaly (00:00:00)</t>
+        <t>-display (12:04:30.837) ~0.71, -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), +dispaly (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E31" authorId="0" shapeId="0">
@@ -387,7 +387,7 @@
     </comment>
     <comment ref="Q31" authorId="0" shapeId="0">
       <text>
-        <t>-} (12:33:32.526), -cells (12:38:41.433), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102), +element (00:00:00)</t>
+        <t>-} (12:33:32.526), -cells (12:38:41.433) ~0.14, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102), +element (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
@@ -402,17 +402,17 @@
     </comment>
     <comment ref="M36" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (11:54:35.668), -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -&gt; (12:25:38.438), -" (12:26:40.406), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +" (00:00:00), +' (00:00:00)</t>
+        <t>-Chess (11:54:35.668) ~0.80, -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953) ~1.00, -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -&gt; (12:25:38.438), -" (12:26:40.406) ~0.00, +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +" (00:00:00), +' (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O36" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:02:47.484), -; (12:02:56.888), -columns (12:05:17.007), -} (12:17:44.771), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -) (12:27:05.426), +: (00:00:00), +: (00:00:00), +coloumns (00:00:00), +height (00:00:00), +50 (00:00:00)</t>
+        <t>-; (12:02:47.484) ~0.00, -; (12:02:56.888) ~0.00, -columns (12:05:17.007) ~0.88, -} (12:17:44.771), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245) ~0.33, -) (12:27:05.426), +: (00:00:00), +: (00:00:00), +coloumns (00:00:00), +height (00:00:00), +50 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q36" authorId="0" shapeId="0">
       <text>
-        <t>-} (12:33:32.526), -getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00)</t>
+        <t>-} (12:33:32.526), -getElementsByClassName (12:37:56.278) ~0.50, -onclick (12:41:03.120) ~0.86, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E45" authorId="0" shapeId="0">
@@ -437,7 +437,7 @@
     </comment>
     <comment ref="Q45" authorId="0" shapeId="0">
       <text>
-        <t>+;* (12:35:18.198), -cells (12:45:13.133), +const* (12:56:52.436), -let (12:56:53.102), +cell (00:00:00)</t>
+        <t>+;* (12:35:18.198), -cells (12:45:13.133) ~0.80, +const* (12:56:52.436), -let (12:56:53.102), +cell (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E46" authorId="0" shapeId="0">
@@ -457,7 +457,7 @@
     </comment>
     <comment ref="M46" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (11:53:34.288), -&gt; (11:58:37.856), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +DOCTYOE (00:00:00)</t>
+        <t>-DOCTYPE (11:53:34.288) ~0.86, -&gt; (11:58:37.856), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +DOCTYOE (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O46" authorId="0" shapeId="0">
@@ -487,7 +487,7 @@
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (11:56:36.040), -/ (11:56:37.399), -dark (11:58:37.525), -dark (12:08:25.473), -dark (12:08:30.373), -dark (12:08:35.273), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +chess (00:00:00), +handleclick (00:00:00), +/ (00:00:00), +div (00:00:00), +class (00:00:00), +&lt; (00:00:00), +light (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +cell (00:00:00), +light (00:00:00), +\ (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00)</t>
+        <t>-Chess (11:56:36.040) ~0.80, -/ (11:56:37.399) ~1.00, -dark (11:58:37.525) ~0.00, -dark (12:08:25.473) ~0.00, -dark (12:08:30.373) ~0.00, -dark (12:08:35.273) ~0.00, -img (12:25:35.614) ~0.00, -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278) ~0.00, -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154) ~0.40, +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +chess (00:00:00), +handleclick (00:00:00), +/ (00:00:00), +div (00:00:00), +class (00:00:00), +&lt; (00:00:00), +light (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +cell (00:00:00), +light (00:00:00), +\ (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O48" authorId="0" shapeId="0">
@@ -522,12 +522,12 @@
     </comment>
     <comment ref="M50" authorId="0" shapeId="0">
       <text>
-        <t>-html (11:53:51.658), -&lt; (11:57:53.359), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +" (00:00:00), +handClick (00:00:00), +htm (00:00:00)</t>
+        <t>-html (11:53:51.658) ~0.75, -&lt; (11:57:53.359), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953) ~1.00, -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +" (00:00:00), +handClick (00:00:00), +htm (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q50" authorId="0" shapeId="0">
       <text>
-        <t>-function (12:33:12.903), -handleClick (12:33:15.189), -( (12:33:15.589), -element (12:33:31.280), -) (12:33:31.506), -{ (12:33:31.963), +;* (12:35:18.198), -getElementsByClassName (12:37:56.278), -for (12:40:04.800), -( (12:40:05.203), -const (12:40:06.186), -cell (12:40:07.141), -of (12:40:07.700), -cells (12:40:08.982), -) (12:40:09.100), -{ (12:40:09.697), -} (12:40:10.504), -cell (12:41:01.994), -. (12:41:02.157), -onclick (12:41:03.120), -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:53:29.626), -let (12:56:53.102), +getElementaryByClassName (00:00:00), +selectededPiece (00:00:00), +function (00:00:00), +handleClick (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +const (00:00:00), +cell (00:00:00), +of (00:00:00), +cells (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +; (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00)</t>
+        <t>-function (12:33:12.903) ~1.00, -handleClick (12:33:15.189) ~1.00, -( (12:33:15.589) ~1.00, -element (12:33:31.280) ~1.00, -) (12:33:31.506) ~1.00, -{ (12:33:31.963) ~1.00, +;* (12:35:18.198), -getElementsByClassName (12:37:56.278) ~0.88, -for (12:40:04.800) ~1.00, -( (12:40:05.203) ~1.00, -const (12:40:06.186) ~1.00, -cell (12:40:07.141) ~1.00, -of (12:40:07.700) ~1.00, -cells (12:40:08.982) ~1.00, -) (12:40:09.100) ~1.00, -{ (12:40:09.697) ~1.00, -} (12:40:10.504), -cell (12:41:01.994) ~0.29, -. (12:41:02.157) ~1.00, -onclick (12:41:03.120) ~0.14, -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:53:29.626) ~0.87, -let (12:56:53.102), +getElementaryByClassName (00:00:00), +selectededPiece (00:00:00), +function (00:00:00), +handleClick (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +const (00:00:00), +cell (00:00:00), +of (00:00:00), +cells (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +; (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E51" authorId="0" shapeId="0">
@@ -562,7 +562,7 @@
     </comment>
     <comment ref="M56" authorId="0" shapeId="0">
       <text>
-        <t>-head (11:54:17.814), -/ (11:57:53.708), -div (11:57:54.317), -&gt; (11:57:54.617), -&lt; (12:32:49.891), +heal (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p6 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +/ (00:00:00)</t>
+        <t>-head (11:54:17.814) ~0.75, -/ (11:57:53.708) ~1.00, -div (11:57:54.317), -&gt; (11:57:54.617), -&lt; (12:32:49.891), +heal (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p6 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +/ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q56" authorId="0" shapeId="0">
@@ -587,22 +587,22 @@
     </comment>
     <comment ref="M59" authorId="0" shapeId="0">
       <text>
-        <t>-! (11:53:33.047), -&lt; (12:01:45.480), -/ (12:01:45.692), -style (12:01:46.591), -&gt; (12:01:46.854), -dark (12:08:22.713), -" (12:08:22.723), -&gt; (12:08:22.733), -&lt; (12:08:22.743), -/ (12:08:22.753), -div (12:08:22.783), -&gt; (12:08:22.793), -&lt; (12:08:22.813), -div (12:08:22.843), -class (12:08:22.903), -= (12:08:22.913), -" (12:08:22.923), -cell (12:08:22.963), -" (12:08:23.333), -&gt; (12:08:23.343), -&lt; (12:08:23.353), -/ (12:08:23.363), -div (12:08:23.393), -&gt; (12:08:23.403), -&lt; (12:08:23.423), -div (12:08:23.453), -class (12:08:23.513), -= (12:08:23.523), -" (12:08:23.533), -cell (12:08:23.573), -light (12:08:23.633), -" (12:08:23.643), -&gt; (12:08:23.653), -&lt; (12:08:23.663), -/ (12:08:23.673), -div (12:08:23.703), -&gt; (12:08:23.713), -&lt; (12:08:23.733), -div (12:08:23.763), -class (12:08:23.823), -= (12:08:23.833), -" (12:08:23.843), -cell (12:08:23.883), -dark (12:08:23.933), -" (12:08:23.943), -&gt; (12:08:23.953), -&lt; (12:08:23.963), -/ (12:08:23.973), -div (12:08:24.003), -&gt; (12:08:24.013), -&lt; (12:08:24.033), -div (12:08:24.063), -class (12:08:24.123), -= (12:08:24.133), -" (12:08:24.143), -cell (12:08:24.183), -light (12:08:24.243), -" (12:08:24.253), -&gt; (12:08:24.263), -&lt; (12:08:24.273), -/ (12:08:24.283), -div (12:08:24.313), -&gt; (12:08:24.323), -&lt; (12:08:24.343), -div (12:08:24.373), -class (12:08:24.433), -= (12:08:24.443), -" (12:08:24.453), -cell (12:08:24.493), -dark (12:08:24.543), -" (12:08:24.553), -&gt; (12:08:24.563), -&lt; (12:08:24.573), -/ (12:08:24.583), -div (12:08:24.613), -&gt; (12:08:24.623), -&lt; (12:08:24.643), -div (12:08:24.673), -class (12:08:24.733), -= (12:08:24.743), -" (12:08:24.753), -cell (12:08:24.793), -light (12:08:24.853), -dark (12:08:27.613), -" (12:08:27.623), -&gt; (12:08:27.633), -&lt; (12:08:27.643), -/ (12:08:27.653), -div (12:08:27.683), -&gt; (12:08:27.693), -&lt; (12:08:27.713), -div (12:08:27.743), -class (12:08:27.803), -= (12:08:27.813), -" (12:08:27.823), -cell (12:08:27.863), -" (12:08:28.233), -&gt; (12:08:28.243), -&lt; (12:08:28.253), -/ (12:08:28.263), -div (12:08:28.293), -&gt; (12:08:28.303), -&lt; (12:08:28.323), -div (12:08:28.353), -class (12:08:28.413), -= (12:08:28.423), -" (12:08:28.433), -cell (12:08:28.473), -light (12:08:28.533), -" (12:08:28.543), -&gt; (12:08:28.553), -&lt; (12:08:28.563), -/ (12:08:28.573), -div (12:08:28.603), -&gt; (12:08:28.613), -&lt; (12:08:28.633), -div (12:08:28.663), -class (12:08:28.723), -= (12:08:28.733), -" (12:08:28.743), -cell (12:08:28.783), -dark (12:08:28.833), -" (12:08:28.843), -&gt; (12:08:28.853), -&lt; (12:08:28.863), -/ (12:08:28.873), -div (12:08:28.903), -&gt; (12:08:28.913), -&lt; (12:08:28.933), -div (12:08:28.963), -class (12:08:29.023), -= (12:08:29.033), -" (12:08:29.043), -cell (12:08:29.083), -light (12:08:29.143), -" (12:08:29.153), -&gt; (12:08:29.163), -&lt; (12:08:29.173), -/ (12:08:29.183), -div (12:08:29.213), -&gt; (12:08:29.223), -&lt; (12:08:29.243), -div (12:08:29.273), -class (12:08:29.333), -= (12:08:29.343), -" (12:08:29.353), -cell (12:08:29.393), -dark (12:08:29.443), -" (12:08:29.453), -&gt; (12:08:29.463), -&lt; (12:08:29.473), -/ (12:08:29.483), -div (12:08:29.513), -&gt; (12:08:29.523), -&lt; (12:08:29.543), -div (12:08:29.573), -class (12:08:29.633), -= (12:08:29.643), -" (12:08:29.653), -cell (12:08:29.693), -light (12:08:29.753), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), +ing (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00), +} (00:00:00), +. (00:00:00), +invert (00:00:00), +- (00:00:00), +color (00:00:00), +{ (00:00:00), +filter (00:00:00), +: (00:00:00), +invert (00:00:00), +( (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-! (11:53:33.047), -&lt; (12:01:45.480), -/ (12:01:45.692), -style (12:01:46.591), -&gt; (12:01:46.854), -dark (12:08:22.713), -" (12:08:22.723), -&gt; (12:08:22.733), -&lt; (12:08:22.743), -/ (12:08:22.753), -div (12:08:22.783), -&gt; (12:08:22.793), -&lt; (12:08:22.813), -div (12:08:22.843), -class (12:08:22.903), -= (12:08:22.913), -" (12:08:22.923), -cell (12:08:22.963), -" (12:08:23.333), -&gt; (12:08:23.343), -&lt; (12:08:23.353), -/ (12:08:23.363), -div (12:08:23.393), -&gt; (12:08:23.403), -&lt; (12:08:23.423), -div (12:08:23.453), -class (12:08:23.513), -= (12:08:23.523), -" (12:08:23.533), -cell (12:08:23.573), -light (12:08:23.633), -" (12:08:23.643), -&gt; (12:08:23.653), -&lt; (12:08:23.663), -/ (12:08:23.673), -div (12:08:23.703), -&gt; (12:08:23.713), -&lt; (12:08:23.733), -div (12:08:23.763), -class (12:08:23.823), -= (12:08:23.833), -" (12:08:23.843), -cell (12:08:23.883), -dark (12:08:23.933), -" (12:08:23.943), -&gt; (12:08:23.953), -&lt; (12:08:23.963), -/ (12:08:23.973), -div (12:08:24.003), -&gt; (12:08:24.013), -&lt; (12:08:24.033), -div (12:08:24.063), -class (12:08:24.123), -= (12:08:24.133), -" (12:08:24.143), -cell (12:08:24.183), -light (12:08:24.243), -" (12:08:24.253), -&gt; (12:08:24.263), -&lt; (12:08:24.273), -/ (12:08:24.283), -div (12:08:24.313), -&gt; (12:08:24.323), -&lt; (12:08:24.343), -div (12:08:24.373), -class (12:08:24.433), -= (12:08:24.443), -" (12:08:24.453), -cell (12:08:24.493), -dark (12:08:24.543), -" (12:08:24.553), -&gt; (12:08:24.563), -&lt; (12:08:24.573), -/ (12:08:24.583), -div (12:08:24.613), -&gt; (12:08:24.623), -&lt; (12:08:24.643), -div (12:08:24.673), -class (12:08:24.733), -= (12:08:24.743), -" (12:08:24.753), -cell (12:08:24.793), -light (12:08:24.853), -dark (12:08:27.613), -" (12:08:27.623), -&gt; (12:08:27.633), -&lt; (12:08:27.643), -/ (12:08:27.653), -div (12:08:27.683), -&gt; (12:08:27.693), -&lt; (12:08:27.713), -div (12:08:27.743), -class (12:08:27.803), -= (12:08:27.813), -" (12:08:27.823), -cell (12:08:27.863), -" (12:08:28.233), -&gt; (12:08:28.243), -&lt; (12:08:28.253), -/ (12:08:28.263), -div (12:08:28.293), -&gt; (12:08:28.303), -&lt; (12:08:28.323), -div (12:08:28.353), -class (12:08:28.413), -= (12:08:28.423), -" (12:08:28.433), -cell (12:08:28.473), -light (12:08:28.533), -" (12:08:28.543), -&gt; (12:08:28.553), -&lt; (12:08:28.563), -/ (12:08:28.573), -div (12:08:28.603), -&gt; (12:08:28.613), -&lt; (12:08:28.633), -div (12:08:28.663), -class (12:08:28.723), -= (12:08:28.733), -" (12:08:28.743), -cell (12:08:28.783), -dark (12:08:28.833), -" (12:08:28.843), -&gt; (12:08:28.853), -&lt; (12:08:28.863), -/ (12:08:28.873), -div (12:08:28.903), -&gt; (12:08:28.913), -&lt; (12:08:28.933), -div (12:08:28.963), -class (12:08:29.023), -= (12:08:29.033), -" (12:08:29.043), -cell (12:08:29.083), -light (12:08:29.143), -" (12:08:29.153), -&gt; (12:08:29.163), -&lt; (12:08:29.173), -/ (12:08:29.183), -div (12:08:29.213), -&gt; (12:08:29.223), -&lt; (12:08:29.243), -div (12:08:29.273), -class (12:08:29.333), -= (12:08:29.343), -" (12:08:29.353), -cell (12:08:29.393), -dark (12:08:29.443), -" (12:08:29.453), -&gt; (12:08:29.463), -&lt; (12:08:29.473), -/ (12:08:29.483), -div (12:08:29.513), -&gt; (12:08:29.523), -&lt; (12:08:29.543), -div (12:08:29.573), -class (12:08:29.633), -= (12:08:29.643), -" (12:08:29.653), -cell (12:08:29.693), -light (12:08:29.753), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563) ~1.00, -class (12:08:33.623) ~1.00, -= (12:08:33.633) ~1.00, -" (12:08:33.643) ~1.00, -cell (12:08:33.683) ~1.00, -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053) ~1.00, -&gt; (12:08:34.063) ~1.00, -&lt; (12:08:34.073) ~1.00, -/ (12:08:34.083) ~1.00, -div (12:08:34.113) ~1.00, -&gt; (12:08:34.123) ~1.00, -&lt; (12:08:34.143) ~1.00, -div (12:08:34.173) ~1.00, -class (12:08:34.233) ~1.00, -= (12:08:34.243) ~1.00, -" (12:08:34.253) ~1.00, -cell (12:08:34.293) ~1.00, -dark (12:08:34.343) ~1.00, -" (12:08:34.353) ~1.00, -&gt; (12:08:34.363) ~1.00, -&lt; (12:08:34.373) ~1.00, -/ (12:08:34.383) ~1.00, -div (12:08:34.413) ~1.00, -&gt; (12:08:34.423) ~1.00, -&lt; (12:08:34.443) ~1.00, -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653) ~1.00, +ing (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00), +} (00:00:00), +. (00:00:00), +invert (00:00:00), +- (00:00:00), +color (00:00:00), +{ (00:00:00), +filter (00:00:00), +: (00:00:00), +invert (00:00:00), +( (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O59" authorId="0" shapeId="0">
       <text>
-        <t>-} (12:02:03.928), -; (12:02:47.484), -; (12:02:56.888), -img (12:17:42.332), -{ (12:17:43.944), -} (12:17:44.771), -width (12:17:46.547), -: (12:17:46.642), +;* (12:18:30.043), -50 (12:20:14.705), -% (12:20:15.067), -; (12:20:15.756), -flex (12:24:01.038), -; (12:24:01.089), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), +} (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +; (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +/ (00:00:00), +anonymous (00:00:00), +function (00:00:00), +handleclick (00:00:00), +( (00:00:00), +cell (00:00:00), +) (00:00:00), +console (00:00:00), +. (00:00:00), +long (00:00:00), +element (00:00:00), +; (00:00:00)</t>
+        <t>-} (12:02:03.928), -; (12:02:47.484), -; (12:02:56.888), -img (12:17:42.332) ~0.67, -{ (12:17:43.944) ~1.00, -} (12:17:44.771) ~1.00, -width (12:17:46.547) ~1.00, -: (12:17:46.642) ~1.00, +;* (12:18:30.043), -50 (12:20:14.705) ~1.00, -% (12:20:15.067) ~1.00, -; (12:20:15.756), -flex (12:24:01.038), -; (12:24:01.089) ~1.00, -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -. (12:26:59.213) ~1.00, -invert (12:27:00.293) ~1.00, -- (12:27:00.514) ~1.00, -color (12:27:01.097) ~1.00, -{ (12:27:01.630) ~1.00, -} (12:27:01.824) ~1.00, -filter (12:27:03.521) ~1.00, -: (12:27:03.624) ~1.00, -invert (12:27:04.621) ~1.00, -( (12:27:04.730) ~1.00, -100 (12:27:05.245) ~1.00, -% (12:27:05.347) ~1.00, -) (12:27:05.426) ~1.00, -; (12:27:05.639) ~1.00, +} (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +; (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +/ (00:00:00), +anonymous (00:00:00), +function (00:00:00), +handleclick (00:00:00), +( (00:00:00), +cell (00:00:00), +) (00:00:00), +console (00:00:00), +. (00:00:00), +long (00:00:00), +element (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q59" authorId="0" shapeId="0">
       <text>
-        <t>-} (12:33:32.526), -for (12:45:10.759), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -{ (12:45:13.433), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102)</t>
+        <t>-} (12:33:32.526), -for (12:45:10.759) ~0.25, -const (12:45:11.606) ~0.57, -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133) ~0.14, -{ (12:45:13.433) ~0.00, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102)</t>
       </text>
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="J62" authorId="0" shapeId="0">
@@ -637,7 +637,7 @@
     </comment>
     <comment ref="M66" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (11:53:34.288), -&gt; (11:58:37.856), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +DOCTYOE (00:00:00)</t>
+        <t>-DOCTYPE (11:53:34.288) ~0.86, -&gt; (11:58:37.856), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +DOCTYOE (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O66" authorId="0" shapeId="0">
@@ -647,7 +647,7 @@
     </comment>
     <comment ref="Q66" authorId="0" shapeId="0">
       <text>
-        <t>-} (12:33:32.526), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -selectedPiece (12:52:11.048), +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00)</t>
+        <t>-} (12:33:32.526), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -selectedPiece (12:52:11.048) ~0.92, +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E68" authorId="0" shapeId="0">
@@ -667,17 +667,17 @@
     </comment>
     <comment ref="M68" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (11:53:50.287), -/ (11:53:50.722), -html (11:53:51.658), -&gt; (11:53:52.247), -&lt; (11:54:54.301), -/ (11:54:54.552), -body (11:54:55.321), -&gt; (11:54:55.640), -/ (11:58:31.581), -dark (11:58:37.525), -/ (12:25:38.278), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), +"* (12:49:43.795), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Game (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +black (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +cell (00:00:00), +dark (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00)</t>
+        <t>-&lt; (11:53:50.287), -/ (11:53:50.722), -html (11:53:51.658), -&gt; (11:53:52.247), -&lt; (11:54:54.301), -/ (11:54:54.552), -body (11:54:55.321), -&gt; (11:54:55.640), -/ (11:58:31.581) ~1.00, -dark (11:58:37.525) ~1.00, -/ (12:25:38.278) ~1.00, -invert (12:26:41.264) ~0.17, -- (12:26:41.305) ~0.00, -color (12:26:42.154) ~0.40, +"* (12:49:43.795), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Game (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +black (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +cell (00:00:00), +dark (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O68" authorId="0" shapeId="0">
       <text>
-        <t>-} (12:02:52.276), -gray (12:02:56.667), -; (12:02:56.888), -# (12:03:33.003), -chess (12:03:34.679), -- (12:03:34.891), -board (12:03:35.921), -{ (12:03:45.639), -width (12:03:53.681), -: (12:03:53.818), -400px (12:03:55.740), -; (12:03:56.458), -height (12:03:58.438), -: (12:03:58.649), -400px (12:03:59.637), -; (12:03:59.993), -display (12:04:30.837), -: (12:04:30.966), -grid (12:04:31.833), -; (12:04:31.971), -grid (12:04:33.784), -- (12:04:33.928), -template (12:04:35.620), -- (12:04:35.828), -rows (12:04:36.631), -: (12:04:36.826), -repeat (12:04:38.281), -( (12:04:38.485), -8 (12:04:38.643), -, (12:04:38.821), -1fr (12:04:39.902), -) (12:04:40.295), -; (12:04:41.132), -grid (12:05:13.862), -- (12:05:13.980), -template (12:05:15.274), -- (12:05:15.459), -columns (12:05:17.007), -: (12:05:17.574), -repeat (12:05:19.260), -( (12:05:19.386), -8 (12:05:19.565), -, (12:05:19.720), -1fr (12:05:20.402), -) (12:05:20.749), -} (12:17:44.771), -50 (12:20:14.705), -; (12:20:15.756), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +400px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +400px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +grid (00:00:00), +; (00:00:00), +grid (00:00:00), +- (00:00:00), +template (00:00:00), +- (00:00:00), +columns (00:00:00), +: (00:00:00), +repeat (00:00:00), +( (00:00:00), +8 (00:00:00), +, (00:00:00), +1fr (00:00:00), +) (00:00:00), +; (00:00:00), +grid (00:00:00), +- (00:00:00), +template (00:00:00), +- (00:00:00), +rows (00:00:00), +: (00:00:00), +repeat (00:00:00), +( (00:00:00), +8 (00:00:00), +, (00:00:00), +1fr (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +grey (00:00:00), +60 (00:00:00)</t>
+        <t>-} (12:02:52.276), -gray (12:02:56.667) ~0.75, -; (12:02:56.888), -# (12:03:33.003) ~1.00, -chess (12:03:34.679) ~1.00, -- (12:03:34.891) ~1.00, -board (12:03:35.921) ~1.00, -{ (12:03:45.639) ~1.00, -width (12:03:53.681) ~1.00, -: (12:03:53.818) ~1.00, -400px (12:03:55.740) ~1.00, -; (12:03:56.458) ~1.00, -height (12:03:58.438) ~1.00, -: (12:03:58.649) ~1.00, -400px (12:03:59.637) ~1.00, -; (12:03:59.993) ~1.00, -display (12:04:30.837) ~1.00, -: (12:04:30.966) ~1.00, -grid (12:04:31.833) ~1.00, -; (12:04:31.971) ~1.00, -grid (12:04:33.784) ~1.00, -- (12:04:33.928) ~1.00, -template (12:04:35.620) ~1.00, -- (12:04:35.828) ~1.00, -rows (12:04:36.631) ~0.29, -: (12:04:36.826) ~1.00, -repeat (12:04:38.281) ~1.00, -( (12:04:38.485) ~1.00, -8 (12:04:38.643) ~1.00, -, (12:04:38.821) ~1.00, -1fr (12:04:39.902) ~1.00, -) (12:04:40.295) ~1.00, -; (12:04:41.132) ~1.00, -grid (12:05:13.862) ~1.00, -- (12:05:13.980) ~1.00, -template (12:05:15.274) ~1.00, -- (12:05:15.459) ~1.00, -columns (12:05:17.007) ~0.29, -: (12:05:17.574) ~1.00, -repeat (12:05:19.260) ~1.00, -( (12:05:19.386) ~1.00, -8 (12:05:19.565) ~1.00, -, (12:05:19.720) ~1.00, -1fr (12:05:20.402) ~1.00, -) (12:05:20.749) ~1.00, -} (12:17:44.771), -50 (12:20:14.705), -; (12:20:15.756), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245) ~0.33, -% (12:27:05.347), -) (12:27:05.426), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +400px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +400px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +grid (00:00:00), +; (00:00:00), +grid (00:00:00), +- (00:00:00), +template (00:00:00), +- (00:00:00), +columns (00:00:00), +: (00:00:00), +repeat (00:00:00), +( (00:00:00), +8 (00:00:00), +, (00:00:00), +1fr (00:00:00), +) (00:00:00), +; (00:00:00), +grid (00:00:00), +- (00:00:00), +template (00:00:00), +- (00:00:00), +rows (00:00:00), +: (00:00:00), +repeat (00:00:00), +( (00:00:00), +8 (00:00:00), +, (00:00:00), +1fr (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +grey (00:00:00), +60 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q68" authorId="0" shapeId="0">
       <text>
-        <t>-cells (12:37:50.791), -getElementsByClassName (12:37:56.278), -cell (12:41:05.940), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), -let (12:56:53.102), +board (00:00:00), +getElementById (00:00:00), +this (00:00:00), +selectedpice (00:00:00), += (00:00:00), +replaceChild (00:00:00), +selectedpice (00:00:00), +selectedpice (00:00:00), +selectedpiece (00:00:00), +return (00:00:00), +; (00:00:00)</t>
+        <t>-cells (12:37:50.791), -getElementsByClassName (12:37:56.278) ~0.55, -cell (12:41:05.940) ~0.00, -selectedPiece (12:51:24.571) ~0.08, -= (12:51:25.051) ~1.00, -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:52:11.048) ~0.85, -replaceChildren (12:52:19.891) ~0.80, -selectedPiece (12:52:27.102) ~0.85, -selectedPiece (12:52:30.641) ~0.85, -selectedPiece (12:53:29.626) ~0.92, -let (12:56:53.102), +board (00:00:00), +getElementById (00:00:00), +this (00:00:00), +selectedpice (00:00:00), += (00:00:00), +replaceChild (00:00:00), +selectedpice (00:00:00), +selectedpice (00:00:00), +selectedpiece (00:00:00), +return (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E70" authorId="0" shapeId="0">
@@ -697,17 +697,17 @@
     </comment>
     <comment ref="M70" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (11:54:35.668), -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -&gt; (12:25:38.438), -" (12:26:40.406), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +" (00:00:00), +' (00:00:00)</t>
+        <t>-Chess (11:54:35.668) ~0.80, -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953) ~1.00, -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -&gt; (12:25:38.438), -" (12:26:40.406) ~0.00, +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +" (00:00:00), +' (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O70" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:02:47.484), -; (12:02:56.888), -columns (12:05:17.007), -} (12:17:44.771), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -) (12:27:05.426), +: (00:00:00), +: (00:00:00), +/ (00:00:00), +1 (00:00:00), +fraction (00:00:00), +/ (00:00:00), +coloumns (00:00:00), +height (00:00:00), +50 (00:00:00)</t>
+        <t>-; (12:02:47.484) ~0.00, -; (12:02:56.888) ~0.00, -columns (12:05:17.007) ~0.88, -} (12:17:44.771), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245) ~0.33, -) (12:27:05.426), +: (00:00:00), +: (00:00:00), +/ (00:00:00), +1 (00:00:00), +fraction (00:00:00), +/ (00:00:00), +coloumns (00:00:00), +height (00:00:00), +50 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q70" authorId="0" shapeId="0">
       <text>
-        <t>-getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00), +selectedpiece (00:00:00), +replaceChirldren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00)</t>
+        <t>-getElementsByClassName (12:37:56.278) ~0.50, -onclick (12:41:03.120) ~0.86, -selectedPiece (12:51:24.571) ~0.92, -selectedPiece (12:52:11.048) ~0.92, -replaceChildren (12:52:19.891) ~0.94, -selectedPiece (12:52:27.102) ~0.92, -selectedPiece (12:52:30.641) ~0.92, -selectedPiece (12:53:29.626) ~0.92, +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00), +selectedpiece (00:00:00), +replaceChirldren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E71" authorId="0" shapeId="0">
@@ -727,7 +727,7 @@
     </comment>
     <comment ref="O71" authorId="0" shapeId="0">
       <text>
-        <t>-gray (12:02:56.667), -; (12:05:21.226), +grey (00:00:00)</t>
+        <t>-gray (12:02:56.667) ~0.75, -; (12:05:21.226), +grey (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q71" authorId="0" shapeId="0">
@@ -752,7 +752,7 @@
     </comment>
     <comment ref="M72" authorId="0" shapeId="0">
       <text>
-        <t>-dark (11:58:37.525), -pieces (12:16:05.490), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Pieces (00:00:00), +light (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +cell (00:00:00), +dark (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +anonymous (00:00:00), +function (00:00:00), +Children (00:00:00)</t>
+        <t>-dark (11:58:37.525) ~1.00, -pieces (12:16:05.490) ~0.83, -img (12:25:35.614) ~0.20, -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154) ~0.40, +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Pieces (00:00:00), +light (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +cell (00:00:00), +dark (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +anonymous (00:00:00), +function (00:00:00), +Children (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O72" authorId="0" shapeId="0">
@@ -762,7 +762,7 @@
     </comment>
     <comment ref="Q72" authorId="0" shapeId="0">
       <text>
-        <t>-} (12:33:32.526), -children (12:53:24.251)</t>
+        <t>-} (12:33:32.526), -children (12:53:24.251) ~0.88</t>
       </text>
     </comment>
     <comment ref="E73" authorId="0" shapeId="0">
@@ -777,7 +777,7 @@
     </comment>
     <comment ref="M73" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (11:53:50.287), -/ (11:53:50.722), -html (11:53:51.658), -&gt; (11:53:52.247), -&lt; (11:54:54.301), -/ (11:54:54.552), -body (11:54:55.321), -&gt; (11:54:55.640), -/ (12:16:05.559), -/ (12:25:37.107), -&lt; (12:32:56.391), -/ (12:32:56.665), -script (12:32:57.709), -&gt; (12:32:57.900), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +handleclick (00:00:00), +\ (00:00:00), +\ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00)</t>
+        <t>-&lt; (11:53:50.287), -/ (11:53:50.722), -html (11:53:51.658), -&gt; (11:53:52.247), -&lt; (11:54:54.301), -/ (11:54:54.552), -body (11:54:55.321), -&gt; (11:54:55.640), -/ (12:16:05.559) ~0.00, -/ (12:25:37.107) ~0.00, -&lt; (12:32:56.391), -/ (12:32:56.665), -script (12:32:57.709), -&gt; (12:32:57.900), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +handleclick (00:00:00), +\ (00:00:00), +\ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O73" authorId="0" shapeId="0">
@@ -787,7 +787,7 @@
     </comment>
     <comment ref="Q73" authorId="0" shapeId="0">
       <text>
-        <t>-element (12:33:31.280), -} (12:33:32.526), -element (12:35:29.854), -. (12:35:29.918), -style (12:35:30.684), -. (12:35:30.708), -border (12:35:31.651), -= (12:35:31.979), -" (12:35:32.153), -4px (12:35:32.780), -solid (12:35:33.773), -red (12:35:34.503), -" (12:35:34.724), -; (12:35:34.812), -handleClick (12:41:05.134), -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +handClick (00:00:00), +eleement (00:00:00), +00 (00:00:00)</t>
+        <t>-element (12:33:31.280) ~0.88, -} (12:33:32.526), -element (12:35:29.854), -. (12:35:29.918), -style (12:35:30.684), -. (12:35:30.708), -border (12:35:31.651), -= (12:35:31.979), -" (12:35:32.153), -4px (12:35:32.780), -solid (12:35:33.773), -red (12:35:34.503), -" (12:35:34.724), -; (12:35:34.812), -handleClick (12:41:05.134) ~0.82, -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +handClick (00:00:00), +eleement (00:00:00), +00 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D75" authorId="0" shapeId="0">
@@ -812,7 +812,7 @@
     </comment>
     <comment ref="M75" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (11:53:34.288), -123456 (11:54:38.411), -&gt; (11:58:37.856), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), -&lt; (12:32:56.391), -/ (12:32:56.665), -script (12:32:57.709), -&gt; (12:32:57.900), +DOCTYOE (00:00:00), +654321 (00:00:00)</t>
+        <t>-DOCTYPE (11:53:34.288) ~0.86, -123456 (11:54:38.411) ~0.00, -&gt; (11:58:37.856), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), -&lt; (12:32:56.391), -/ (12:32:56.665), -script (12:32:57.709), -&gt; (12:32:57.900), +DOCTYOE (00:00:00), +654321 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O75" authorId="0" shapeId="0">
@@ -822,7 +822,7 @@
     </comment>
     <comment ref="Q75" authorId="0" shapeId="0">
       <text>
-        <t>-} (12:33:32.526), -getElementsByClassName (12:37:56.278), -handleClick (12:41:05.134), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -} (12:45:14.115), -cell (12:45:15.612), -style (12:45:16.268), -. (12:45:16.371), -border (12:45:17.066), -= (12:45:17.426), -" (12:45:17.580), -" (12:45:17.718), -; (12:45:17.816), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -let (12:56:53.102), +getElementsbyClassName (00:00:00), +handleclick (00:00:00), +console (00:00:00), +log (00:00:00)</t>
+        <t>-} (12:33:32.526), -getElementsByClassName (12:37:56.278) ~0.95, -handleClick (12:41:05.134), -; (12:41:06.130), -function (12:42:53.629) ~0.27, -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606) ~0.57, -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -} (12:45:14.115), -cell (12:45:15.612), -style (12:45:16.268), -. (12:45:16.371), -border (12:45:17.066), -= (12:45:17.426), -" (12:45:17.580), -" (12:45:17.718), -; (12:45:17.816), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -let (12:56:53.102), +getElementsbyClassName (00:00:00), +handleclick (00:00:00), +console (00:00:00), +log (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
@@ -837,7 +837,7 @@
     </comment>
     <comment ref="M78" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (11:54:35.668), -Chess (11:56:36.040), -Game (11:56:37.110), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +chess (00:00:00), +game (00:00:00), +" (00:00:00), +handleclick (00:00:00)</t>
+        <t>-Chess (11:54:35.668) ~0.80, -Chess (11:56:36.040) ~0.80, -Game (11:56:37.110) ~0.75, +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +chess (00:00:00), +game (00:00:00), +" (00:00:00), +handleclick (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O78" authorId="0" shapeId="0">
@@ -847,7 +847,7 @@
     </comment>
     <comment ref="Q78" authorId="0" shapeId="0">
       <text>
-        <t>-handleClick (12:33:15.189), -handleClick (12:41:05.134), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), +selectedpiece (00:00:00), +handleclick (00:00:00), +handleclick (00:00:00), +selectedpiece (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00)</t>
+        <t>-handleClick (12:33:15.189) ~0.91, -handleClick (12:41:05.134) ~0.91, -selectedPiece (12:51:24.571) ~0.92, -selectedPiece (12:52:11.048) ~0.92, -replaceChildren (12:52:19.891) ~0.93, -selectedPiece (12:52:27.102) ~0.92, -selectedPiece (12:52:30.641) ~0.92, -selectedPiece (12:53:29.626) ~0.92, +selectedpiece (00:00:00), +handleclick (00:00:00), +handleclick (00:00:00), +selectedpiece (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E81" authorId="0" shapeId="0">
@@ -892,12 +892,12 @@
     </comment>
     <comment ref="M82" authorId="0" shapeId="0">
       <text>
-        <t>-/ (12:16:06.943), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p6 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p4 (00:00:00), +. (00:00:00), +png (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p3 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p6 (00:00:00), +. (00:00:00), +png (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p5 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p2 (00:00:00), +. (00:00:00), +png (00:00:00)</t>
+        <t>-/ (12:16:06.943) ~1.00, +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p6 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p4 (00:00:00), +. (00:00:00), +png (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p3 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p6 (00:00:00), +. (00:00:00), +png (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p5 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p2 (00:00:00), +. (00:00:00), +png (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O82" authorId="0" shapeId="0">
       <text>
-        <t>-} (12:03:46.236), -; (12:05:21.226), -img (12:17:42.332), -{ (12:17:43.944), -width (12:17:46.547), -: (12:17:46.642), -50 (12:20:14.705), -% (12:20:15.067), -; (12:20:15.756), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +; (00:00:00), +} (00:00:00), +img (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00)</t>
+        <t>-} (12:03:46.236) ~1.00, -; (12:05:21.226) ~1.00, -img (12:17:42.332) ~1.00, -{ (12:17:43.944) ~1.00, -width (12:17:46.547) ~1.00, -: (12:17:46.642), -50 (12:20:14.705) ~1.00, -% (12:20:15.067) ~1.00, -; (12:20:15.756), -: (12:24:02.925) ~1.00, -center (12:24:03.906) ~1.00, -; (12:24:04.138) ~1.00, -justify (12:24:05.215) ~1.00, -- (12:24:05.313) ~1.00, -content (12:24:06.156) ~1.00, +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +; (00:00:00), +} (00:00:00), +img (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q82" authorId="0" shapeId="0">
@@ -922,7 +922,7 @@
     </comment>
     <comment ref="M83" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (11:54:35.668), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +" (00:00:00), +handelClick (00:00:00)</t>
+        <t>-Chess (11:54:35.668) ~0.80, +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +" (00:00:00), +handelClick (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O83" authorId="0" shapeId="0">
@@ -932,7 +932,7 @@
     </comment>
     <comment ref="Q83" authorId="0" shapeId="0">
       <text>
-        <t>-handleClick (12:33:15.189), +const* (12:56:52.436), -let (12:56:53.102), +handelClick (00:00:00)</t>
+        <t>-handleClick (12:33:15.189) ~0.82, +const* (12:56:52.436), -let (12:56:53.102), +handelClick (00:00:00)</t>
       </text>
     </comment>
   </commentList>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>+;* (12:35:18.198), -border (12:35:31.651), -document (12:37:53.239), -border (12:45:17.066), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00), +documnet (00:00:00), +broder (00:00:00), +selectedpiece (00:00:00), +replace (00:00:00), +Children (00:00:00), +selectedpisce (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +broder (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +broder (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00)</t>
+          <t>+;* (12:35:18.198), -border (12:35:31.651) ~0.67, -document (12:37:53.239) ~0.75, -border (12:45:17.066) ~0.67, -selectedPiece (12:51:24.571) ~0.92, -selectedPiece (12:52:11.048) ~0.92, -replaceChildren (12:52:19.891) ~0.47, -selectedPiece (12:52:27.102) ~0.85, -selectedPiece (12:52:30.641) ~0.92, -selectedPiece (12:53:29.626) ~0.92, +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00), +documnet (00:00:00), +broder (00:00:00), +selectedpiece (00:00:00), +replace (00:00:00), +Children (00:00:00), +selectedpisce (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +broder (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +broder (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-DOCTYPE (11:53:34.288), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +DOCTYOE (00:00:00), +handleclick (00:00:00)</t>
+          <t>-DOCTYPE (11:53:34.288) ~0.86, +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +DOCTYOE (00:00:00), +handleclick (00:00:00)</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-handleClick (12:33:15.189), -} (12:33:32.526), -handleClick (12:41:05.134), -selectedPiece (12:51:24.571), +const* (12:56:52.436), -let (12:56:53.102), +selectedpPiece (00:00:00), +handleclick (00:00:00), +hanleclick (00:00:00)</t>
+          <t>-handleClick (12:33:15.189) ~0.82, -} (12:33:32.526), -handleClick (12:41:05.134) ~0.91, -selectedPiece (12:51:24.571) ~0.93, +const* (12:56:52.436), -let (12:56:53.102), +selectedpPiece (00:00:00), +handleclick (00:00:00), +hanleclick (00:00:00)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-&lt; (11:57:53.359), -&lt; (11:58:31.329), -/ (11:58:31.581), -div (11:58:32.273), -&gt; (11:58:32.462), -&lt; (11:58:34.148), -div (11:58:34.737), -class (11:58:35.647), -= (11:58:35.832), -" (11:58:35.965), -cell (11:58:36.694), -dark (11:58:37.525), -" (11:58:37.701), -&gt; (11:58:37.856), -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -&gt; (12:08:20.903), -&lt; (12:08:20.913), -/ (12:08:20.923), -div (12:08:20.953), -&gt; (12:08:20.963), -&lt; (12:08:20.983), -div (12:08:21.013), -class (12:08:21.073), -= (12:08:21.083), -" (12:08:21.093), -cell (12:08:21.133), -dark (12:08:21.183), -" (12:08:21.193), -&gt; (12:08:21.203), -&lt; (12:08:21.213), -/ (12:08:21.223), -div (12:08:21.253), -&gt; (12:08:21.263), -&lt; (12:08:21.283), -div (12:08:21.313), -class (12:08:21.373), -= (12:08:21.383), -" (12:08:21.393), -cell (12:08:21.433), -light (12:08:21.493), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -" (12:08:22.413), -div (12:08:24.673), -class (12:08:24.733), -= (12:08:24.743), -" (12:08:24.753), -cell (12:08:24.793), -light (12:08:24.853), -" (12:08:24.863), -&gt; (12:08:24.873), -&lt; (12:08:24.883), -/ (12:08:24.893), -div (12:08:24.923), -&gt; (12:08:24.933), -&lt; (12:08:24.963), -div (12:08:24.993), -class (12:08:25.053), -= (12:08:25.063), -" (12:08:25.073), -cell (12:08:25.113), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -dark (12:08:25.473), -" (12:08:25.483), -&gt; (12:08:25.493), -&lt; (12:08:25.503), -/ (12:08:25.513), -div (12:08:25.543), -&gt; (12:08:25.553), -&lt; (12:08:25.573), -div (12:08:25.603), -class (12:08:25.663), -= (12:08:25.673), -" (12:08:25.683), -cell (12:08:25.723), -light (12:08:25.783), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -" (12:08:27.313), -&gt; (12:08:27.323), -&lt; (12:08:27.333), -/ (12:08:27.343), -div (12:08:27.373), -&gt; (12:08:27.383), -&lt; (12:08:27.413), -div (12:08:27.443), -class (12:08:27.503), -= (12:08:27.513), -" (12:08:27.523), -cell (12:08:27.563), -dark (12:08:27.613), -" (12:08:27.623), -&gt; (12:08:27.633), -&lt; (12:08:27.643), -/ (12:08:27.653), -div (12:08:27.683), -&gt; (12:08:27.693), -&lt; (12:08:27.713), -div (12:08:27.743), -class (12:08:27.803), -= (12:08:27.813), -" (12:08:27.823), -cell (12:08:27.863), -light (12:08:27.923), -" (12:08:27.933), -&gt; (12:08:27.943), -&lt; (12:08:27.953), -/ (12:08:27.963), -div (12:08:27.993), -&gt; (12:08:28.003), -&lt; (12:08:28.023), -div (12:08:28.053), -class (12:08:28.113), -= (12:08:28.123), -" (12:08:28.133), -cell (12:08:28.173), -dark (12:08:28.223), -" (12:08:28.233), -&gt; (12:08:28.243), -&lt; (12:08:28.253), -/ (12:08:28.263), -div (12:08:28.293), -&gt; (12:08:28.303), -&lt; (12:08:28.323), -div (12:08:28.353), -class (12:08:28.413), -= (12:08:28.423), -" (12:08:28.433), -cell (12:08:28.473), -light (12:08:28.533), -" (12:08:28.543), -&gt; (12:08:28.553), -&lt; (12:08:28.563), -/ (12:08:28.573), -div (12:08:28.603), -&gt; (12:08:28.613), -&lt; (12:08:28.633), -div (12:08:28.663), -class (12:08:28.723), -= (12:08:28.733), -" (12:08:28.743), -cell (12:08:28.783), -dark (12:08:28.833), -" (12:08:28.843), -&gt; (12:08:28.853), -&lt; (12:08:28.863), -/ (12:08:28.873), -div (12:08:28.903), -&gt; (12:08:28.913), -&lt; (12:08:28.933), -div (12:08:28.963), -class (12:08:29.023), -= (12:08:29.033), -" (12:08:29.043), -cell (12:08:29.083), -light (12:08:29.143), -" (12:08:29.153), -&gt; (12:08:29.163), -&lt; (12:08:29.173), -/ (12:08:29.183), -div (12:08:29.213), -&gt; (12:08:29.223), -&lt; (12:08:29.243), -div (12:08:29.273), -class (12:08:29.333), -= (12:08:29.343), -" (12:08:29.353), -cell (12:08:29.393), -dark (12:08:29.443), -" (12:08:29.453), -&gt; (12:08:29.463), -&lt; (12:08:29.473), -/ (12:08:29.483), -div (12:08:29.513), -&gt; (12:08:29.523), -&lt; (12:08:29.543), -div (12:08:29.573), -class (12:08:29.633), -= (12:08:29.643), -" (12:08:29.653), -cell (12:08:29.693), -light (12:08:29.753), -" (12:08:29.763), -&gt; (12:08:29.773), -&lt; (12:08:29.783), -/ (12:08:29.793), -div (12:08:29.823), -&gt; (12:08:29.833), -&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -/ (12:16:05.559), -p2 (12:16:05.801), -&gt; (12:16:07.243), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +c (00:00:00), +: (00:00:00), +\ (00:00:00), +\ (00:00:00), +pieces (00:00:00), +\ (00:00:00), +rook (00:00:00), +. (00:00:00), +png (00:00:00)</t>
+          <t>-&lt; (11:57:53.359), -&lt; (11:58:31.329), -/ (11:58:31.581), -div (11:58:32.273), -&gt; (11:58:32.462), -&lt; (11:58:34.148), -div (11:58:34.737), -class (11:58:35.647), -= (11:58:35.832), -" (11:58:35.965), -cell (11:58:36.694), -dark (11:58:37.525), -" (11:58:37.701), -&gt; (11:58:37.856), -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -&gt; (12:08:20.903), -&lt; (12:08:20.913), -/ (12:08:20.923), -div (12:08:20.953), -&gt; (12:08:20.963), -&lt; (12:08:20.983), -div (12:08:21.013), -class (12:08:21.073), -= (12:08:21.083), -" (12:08:21.093), -cell (12:08:21.133), -dark (12:08:21.183), -" (12:08:21.193), -&gt; (12:08:21.203), -&lt; (12:08:21.213), -/ (12:08:21.223), -div (12:08:21.253), -&gt; (12:08:21.263), -&lt; (12:08:21.283), -div (12:08:21.313), -class (12:08:21.373), -= (12:08:21.383), -" (12:08:21.393), -cell (12:08:21.433), -light (12:08:21.493), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -" (12:08:22.413), -div (12:08:24.673), -class (12:08:24.733), -= (12:08:24.743), -" (12:08:24.753), -cell (12:08:24.793), -light (12:08:24.853), -" (12:08:24.863), -&gt; (12:08:24.873), -&lt; (12:08:24.883), -/ (12:08:24.893), -div (12:08:24.923), -&gt; (12:08:24.933), -&lt; (12:08:24.963), -div (12:08:24.993), -class (12:08:25.053), -= (12:08:25.063), -" (12:08:25.073), -cell (12:08:25.113), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -dark (12:08:25.473), -" (12:08:25.483), -&gt; (12:08:25.493), -&lt; (12:08:25.503), -/ (12:08:25.513), -div (12:08:25.543), -&gt; (12:08:25.553), -&lt; (12:08:25.573), -div (12:08:25.603), -class (12:08:25.663), -= (12:08:25.673), -" (12:08:25.683), -cell (12:08:25.723), -light (12:08:25.783), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -" (12:08:27.313), -&gt; (12:08:27.323), -&lt; (12:08:27.333), -/ (12:08:27.343), -div (12:08:27.373), -&gt; (12:08:27.383), -&lt; (12:08:27.413), -div (12:08:27.443), -class (12:08:27.503), -= (12:08:27.513), -" (12:08:27.523), -cell (12:08:27.563), -dark (12:08:27.613), -" (12:08:27.623), -&gt; (12:08:27.633), -&lt; (12:08:27.643), -/ (12:08:27.653), -div (12:08:27.683), -&gt; (12:08:27.693), -&lt; (12:08:27.713), -div (12:08:27.743), -class (12:08:27.803), -= (12:08:27.813), -" (12:08:27.823), -cell (12:08:27.863), -light (12:08:27.923), -" (12:08:27.933), -&gt; (12:08:27.943), -&lt; (12:08:27.953), -/ (12:08:27.963), -div (12:08:27.993), -&gt; (12:08:28.003), -&lt; (12:08:28.023), -div (12:08:28.053), -class (12:08:28.113), -= (12:08:28.123), -" (12:08:28.133), -cell (12:08:28.173), -dark (12:08:28.223), -" (12:08:28.233), -&gt; (12:08:28.243), -&lt; (12:08:28.253), -/ (12:08:28.263), -div (12:08:28.293), -&gt; (12:08:28.303), -&lt; (12:08:28.323), -div (12:08:28.353), -class (12:08:28.413), -= (12:08:28.423), -" (12:08:28.433), -cell (12:08:28.473), -light (12:08:28.533), -" (12:08:28.543), -&gt; (12:08:28.553), -&lt; (12:08:28.563), -/ (12:08:28.573), -div (12:08:28.603), -&gt; (12:08:28.613), -&lt; (12:08:28.633), -div (12:08:28.663), -class (12:08:28.723), -= (12:08:28.733), -" (12:08:28.743), -cell (12:08:28.783), -dark (12:08:28.833), -" (12:08:28.843), -&gt; (12:08:28.853), -&lt; (12:08:28.863), -/ (12:08:28.873), -div (12:08:28.903), -&gt; (12:08:28.913), -&lt; (12:08:28.933), -div (12:08:28.963), -class (12:08:29.023), -= (12:08:29.033), -" (12:08:29.043), -cell (12:08:29.083), -light (12:08:29.143), -" (12:08:29.153), -&gt; (12:08:29.163), -&lt; (12:08:29.173), -/ (12:08:29.183), -div (12:08:29.213), -&gt; (12:08:29.223), -&lt; (12:08:29.243), -div (12:08:29.273), -class (12:08:29.333), -= (12:08:29.343), -" (12:08:29.353), -cell (12:08:29.393), -dark (12:08:29.443), -" (12:08:29.453), -&gt; (12:08:29.463), -&lt; (12:08:29.473), -/ (12:08:29.483), -div (12:08:29.513), -&gt; (12:08:29.523), -&lt; (12:08:29.543), -div (12:08:29.573), -class (12:08:29.633), -= (12:08:29.643), -" (12:08:29.653), -cell (12:08:29.693), -light (12:08:29.753), -" (12:08:29.763), -&gt; (12:08:29.773), -&lt; (12:08:29.783), -/ (12:08:29.793), -div (12:08:29.823), -&gt; (12:08:29.833), -&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -/ (12:16:05.559), -p2 (12:16:05.801) ~0.33, -&gt; (12:16:07.243), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +c (00:00:00), +: (00:00:00), +\ (00:00:00), +\ (00:00:00), +pieces (00:00:00), +\ (00:00:00), +rook (00:00:00), +. (00:00:00), +png (00:00:00)</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-width (12:03:53.681), -: (12:03:53.818), -400px (12:03:55.740), -; (12:03:56.458), -height (12:03:58.438), -: (12:03:58.649), -400px (12:03:59.637), -; (12:03:59.993), -1fr (12:04:39.902), -1fr (12:05:20.402), -} (12:17:44.771), -50 (12:20:14.705), -display (12:24:00.258), -flex (12:24:01.038), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621), -( (12:27:04.730), -) (12:27:05.426), +width (00:00:00), +50px (00:00:00), +height (00:00:00), +50px (00:00:00), +50px (00:00:00), +50px (00:00:00), +100 (00:00:00), +height (00:00:00)</t>
+          <t>-width (12:03:53.681), -: (12:03:53.818), -400px (12:03:55.740), -; (12:03:56.458), -height (12:03:58.438), -: (12:03:58.649), -400px (12:03:59.637), -; (12:03:59.993), -1fr (12:04:39.902) ~0.00, -1fr (12:05:20.402) ~0.00, -} (12:17:44.771), -50 (12:20:14.705) ~0.33, -display (12:24:00.258) ~0.14, -flex (12:24:01.038) ~0.25, -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000) ~0.00, -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621) ~0.17, -( (12:27:04.730), -) (12:27:05.426), +width (00:00:00), +50px (00:00:00), +height (00:00:00), +50px (00:00:00), +50px (00:00:00), +50px (00:00:00), +100 (00:00:00), +height (00:00:00)</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-} (12:33:32.526), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102), +) (00:00:00), +; (00:00:00), +let (00:00:00), +selectedPiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +const (00:00:00), +cells (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +cell (00:00:00), +" (00:00:00), +if (00:00:00), +( (00:00:00), +selectedPiece (00:00:00), +! (00:00:00), += (00:00:00), +null (00:00:00), +) (00:00:00), +{ (00:00:00), +element (00:00:00), +. (00:00:00), +replaceChildren (00:00:00), +( (00:00:00), +selectdPiece (00:00:00), +) (00:00:00), +; (00:00:00), +selectedPiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +if (00:00:00), +( (00:00:00), +element (00:00:00), +. (00:00:00), +children (00:00:00), +. (00:00:00), +length (00:00:00), +&gt; (00:00:00), +0 (00:00:00), +) (00:00:00), +{ (00:00:00), +selectedPeiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-} (12:33:32.526), -selectedPiece (12:51:24.571) ~1.00, -= (12:51:25.051) ~1.00, -null (12:51:25.997) ~1.00, -; (12:51:26.172) ~1.00, -if (12:52:09.187) ~1.00, -( (12:52:09.526) ~1.00, -selectedPiece (12:52:11.048) ~1.00, -! (12:52:11.221) ~1.00, -= (12:52:11.422) ~1.00, -null (12:52:12.167) ~1.00, -) (12:52:12.282) ~1.00, -{ (12:52:13.202) ~1.00, -} (12:52:13.907) ~1.00, -element (12:52:17.350) ~1.00, -. (12:52:17.520) ~1.00, -replaceChildren (12:52:19.891) ~1.00, -( (12:52:20.134) ~1.00, -selectedPiece (12:52:27.102) ~0.92, -) (12:52:27.322) ~1.00, -; (12:52:27.519) ~1.00, -selectedPiece (12:52:30.641) ~1.00, -= (12:52:30.798) ~1.00, -null (12:52:31.700) ~1.00, -; (12:52:31.752) ~1.00, -else (12:53:21.083) ~1.00, -if (12:53:21.591) ~1.00, -( (12:53:21.914) ~1.00, -element (12:53:22.881) ~1.00, -. (12:53:23.171) ~1.00, -children (12:53:24.251) ~1.00, -. (12:53:24.441) ~1.00, -length (12:53:25.380) ~1.00, -&gt; (12:53:25.564) ~1.00, -0 (12:53:25.976) ~1.00, -) (12:53:26.161) ~1.00, -{ (12:53:26.816) ~1.00, -selectedPiece (12:53:29.626) ~0.93, -= (12:53:29.829) ~1.00, -element (12:53:30.892) ~1.00, -. (12:53:31.019) ~1.00, -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598) ~0.00, -; (12:53:33.056) ~1.00, -let (12:56:53.102) ~1.00, +) (00:00:00), +; (00:00:00), +let (00:00:00), +selectedPiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +const (00:00:00), +cells (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +cell (00:00:00), +" (00:00:00), +if (00:00:00), +( (00:00:00), +selectedPiece (00:00:00), +! (00:00:00), += (00:00:00), +null (00:00:00), +) (00:00:00), +{ (00:00:00), +element (00:00:00), +. (00:00:00), +replaceChildren (00:00:00), +( (00:00:00), +selectdPiece (00:00:00), +) (00:00:00), +; (00:00:00), +selectedPiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +if (00:00:00), +( (00:00:00), +element (00:00:00), +. (00:00:00), +children (00:00:00), +. (00:00:00), +length (00:00:00), +&gt; (00:00:00), +0 (00:00:00), +) (00:00:00), +{ (00:00:00), +selectedPeiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-" (12:25:37.915), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +class (00:00:00), += (00:00:00), +" (00:00:00), +invert (00:00:00), +- (00:00:00), +color (00:00:00), +" (00:00:00)</t>
+          <t>-" (12:25:37.915) ~1.00, -class (12:26:40.137) ~1.00, -= (12:26:40.349) ~1.00, -" (12:26:40.406), -invert (12:26:41.264) ~1.00, -- (12:26:41.305) ~1.00, -color (12:26:42.154) ~1.00, +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +class (00:00:00), += (00:00:00), +" (00:00:00), +invert (00:00:00), +- (00:00:00), +color (00:00:00), +" (00:00:00)</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>-border (12:35:31.651), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -let (12:56:53.102), +boder (00:00:00)</t>
+          <t>-border (12:35:31.651) ~0.83, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -let (12:56:53.102), +boder (00:00:00)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-DOCTYPE (11:53:34.288), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Doctype (00:00:00), +" (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00)</t>
+          <t>-DOCTYPE (11:53:34.288) ~0.14, +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Doctype (00:00:00), +" (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00)</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-gray (12:02:56.667), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +grey (00:00:00)</t>
+          <t>-gray (12:02:56.667) ~0.75, -: (12:24:02.925) ~1.00, -center (12:24:03.906) ~1.00, -; (12:24:04.138) ~1.00, -justify (12:24:05.215) ~1.00, -- (12:24:05.313) ~1.00, -content (12:24:06.156) ~1.00, +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +grey (00:00:00)</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-DOCTYPE (11:53:34.288), -Chess (11:54:35.668), -/ (12:16:06.943), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Doctype (00:00:00), +chess (00:00:00), +handleclick (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00)</t>
+          <t>-DOCTYPE (11:53:34.288) ~0.14, -Chess (11:54:35.668) ~0.80, -/ (12:16:06.943) ~1.00, +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Doctype (00:00:00), +chess (00:00:00), +handleclick (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00)</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-gray (12:02:56.667), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), +grey (00:00:00)</t>
+          <t>-gray (12:02:56.667) ~0.75, -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), +grey (00:00:00)</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>-handleClick (12:33:15.189), -handleClick (12:41:05.134), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -length (12:53:25.380), -selectedPiece (12:53:29.626), +const* (12:56:52.436), -let (12:56:53.102), +selectedpice (00:00:00), +handleclick (00:00:00), +handleclick (00:00:00), +selectedpiece (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +lenght (00:00:00), +selectedpiece (00:00:00)</t>
+          <t>-handleClick (12:33:15.189) ~0.91, -handleClick (12:41:05.134) ~0.91, -selectedPiece (12:51:24.571) ~0.85, -selectedPiece (12:52:11.048) ~0.92, -replaceChildren (12:52:19.891) ~0.93, -selectedPiece (12:52:27.102) ~0.92, -selectedPiece (12:52:30.641) ~0.92, -length (12:53:25.380) ~0.67, -selectedPiece (12:53:29.626) ~0.92, +const* (12:56:52.436), -let (12:56:53.102), +selectedpice (00:00:00), +handleclick (00:00:00), +handleclick (00:00:00), +selectedpiece (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +lenght (00:00:00), +selectedpiece (00:00:00)</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-display (12:04:30.837), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), +dispaly (00:00:00)</t>
+          <t>-display (12:04:30.837) ~0.71, -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), +dispaly (00:00:00)</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>-} (12:33:32.526), -cells (12:38:41.433), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102), +element (00:00:00)</t>
+          <t>-} (12:33:32.526), -cells (12:38:41.433) ~0.14, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102), +element (00:00:00)</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-Chess (11:54:35.668), -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -&gt; (12:25:38.438), -" (12:26:40.406), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +" (00:00:00), +' (00:00:00)</t>
+          <t>-Chess (11:54:35.668) ~0.80, -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953) ~1.00, -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -&gt; (12:25:38.438), -" (12:26:40.406) ~0.00, +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +" (00:00:00), +' (00:00:00)</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-; (12:02:47.484), -; (12:02:56.888), -columns (12:05:17.007), -} (12:17:44.771), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -) (12:27:05.426), +: (00:00:00), +: (00:00:00), +coloumns (00:00:00), +height (00:00:00), +50 (00:00:00)</t>
+          <t>-; (12:02:47.484) ~0.00, -; (12:02:56.888) ~0.00, -columns (12:05:17.007) ~0.88, -} (12:17:44.771), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245) ~0.33, -) (12:27:05.426), +: (00:00:00), +: (00:00:00), +coloumns (00:00:00), +height (00:00:00), +50 (00:00:00)</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-} (12:33:32.526), -getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00)</t>
+          <t>-} (12:33:32.526), -getElementsByClassName (12:37:56.278) ~0.50, -onclick (12:41:03.120) ~0.86, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>+;* (12:35:18.198), -cells (12:45:13.133), +const* (12:56:52.436), -let (12:56:53.102), +cell (00:00:00)</t>
+          <t>+;* (12:35:18.198), -cells (12:45:13.133) ~0.80, +const* (12:56:52.436), -let (12:56:53.102), +cell (00:00:00)</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-DOCTYPE (11:53:34.288), -&gt; (11:58:37.856), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +DOCTYOE (00:00:00)</t>
+          <t>-DOCTYPE (11:53:34.288) ~0.86, -&gt; (11:58:37.856), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +DOCTYOE (00:00:00)</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-Chess (11:56:36.040), -/ (11:56:37.399), -dark (11:58:37.525), -dark (12:08:25.473), -dark (12:08:30.373), -dark (12:08:35.273), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +chess (00:00:00), +handleclick (00:00:00), +/ (00:00:00), +div (00:00:00), +class (00:00:00), +&lt; (00:00:00), +light (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +cell (00:00:00), +light (00:00:00), +\ (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00)</t>
+          <t>-Chess (11:56:36.040) ~0.80, -/ (11:56:37.399) ~1.00, -dark (11:58:37.525) ~0.00, -dark (12:08:25.473) ~0.00, -dark (12:08:30.373) ~0.00, -dark (12:08:35.273) ~0.00, -img (12:25:35.614) ~0.00, -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278) ~0.00, -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154) ~0.40, +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +chess (00:00:00), +handleclick (00:00:00), +/ (00:00:00), +div (00:00:00), +class (00:00:00), +&lt; (00:00:00), +light (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +cell (00:00:00), +light (00:00:00), +\ (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00)</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>-html (11:53:51.658), -&lt; (11:57:53.359), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +" (00:00:00), +handClick (00:00:00), +htm (00:00:00)</t>
+          <t>-html (11:53:51.658) ~0.75, -&lt; (11:57:53.359), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953) ~1.00, -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +" (00:00:00), +handClick (00:00:00), +htm (00:00:00)</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>-function (12:33:12.903), -handleClick (12:33:15.189), -( (12:33:15.589), -element (12:33:31.280), -) (12:33:31.506), -{ (12:33:31.963), +;* (12:35:18.198), -getElementsByClassName (12:37:56.278), -for (12:40:04.800), -( (12:40:05.203), -const (12:40:06.186), -cell (12:40:07.141), -of (12:40:07.700), -cells (12:40:08.982), -) (12:40:09.100), -{ (12:40:09.697), -} (12:40:10.504), -cell (12:41:01.994), -. (12:41:02.157), -onclick (12:41:03.120), -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:53:29.626), -let (12:56:53.102), +getElementaryByClassName (00:00:00), +selectededPiece (00:00:00), +function (00:00:00), +handleClick (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +const (00:00:00), +cell (00:00:00), +of (00:00:00), +cells (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +; (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00)</t>
+          <t>-function (12:33:12.903) ~1.00, -handleClick (12:33:15.189) ~1.00, -( (12:33:15.589) ~1.00, -element (12:33:31.280) ~1.00, -) (12:33:31.506) ~1.00, -{ (12:33:31.963) ~1.00, +;* (12:35:18.198), -getElementsByClassName (12:37:56.278) ~0.88, -for (12:40:04.800) ~1.00, -( (12:40:05.203) ~1.00, -const (12:40:06.186) ~1.00, -cell (12:40:07.141) ~1.00, -of (12:40:07.700) ~1.00, -cells (12:40:08.982) ~1.00, -) (12:40:09.100) ~1.00, -{ (12:40:09.697) ~1.00, -} (12:40:10.504), -cell (12:41:01.994) ~0.29, -. (12:41:02.157) ~1.00, -onclick (12:41:03.120) ~0.14, -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:53:29.626) ~0.87, -let (12:56:53.102), +getElementaryByClassName (00:00:00), +selectededPiece (00:00:00), +function (00:00:00), +handleClick (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +const (00:00:00), +cell (00:00:00), +of (00:00:00), +cells (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +; (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00)</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>-head (11:54:17.814), -/ (11:57:53.708), -div (11:57:54.317), -&gt; (11:57:54.617), -&lt; (12:32:49.891), +heal (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p6 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +/ (00:00:00)</t>
+          <t>-head (11:54:17.814) ~0.75, -/ (11:57:53.708) ~1.00, -div (11:57:54.317), -&gt; (11:57:54.617), -&lt; (12:32:49.891), +heal (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p6 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +/ (00:00:00)</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>-! (11:53:33.047), -&lt; (12:01:45.480), -/ (12:01:45.692), -style (12:01:46.591), -&gt; (12:01:46.854), -dark (12:08:22.713), -" (12:08:22.723), -&gt; (12:08:22.733), -&lt; (12:08:22.743), -/ (12:08:22.753), -div (12:08:22.783), -&gt; (12:08:22.793), -&lt; (12:08:22.813), -div (12:08:22.843), -class (12:08:22.903), -= (12:08:22.913), -" (12:08:22.923), -cell (12:08:22.963), -" (12:08:23.333), -&gt; (12:08:23.343), -&lt; (12:08:23.353), -/ (12:08:23.363), -div (12:08:23.393), -&gt; (12:08:23.403), -&lt; (12:08:23.423), -div (12:08:23.453), -class (12:08:23.513), -= (12:08:23.523), -" (12:08:23.533), -cell (12:08:23.573), -light (12:08:23.633), -" (12:08:23.643), -&gt; (12:08:23.653), -&lt; (12:08:23.663), -/ (12:08:23.673), -div (12:08:23.703), -&gt; (12:08:23.713), -&lt; (12:08:23.733), -div (12:08:23.763), -class (12:08:23.823), -= (12:08:23.833), -" (12:08:23.843), -cell (12:08:23.883), -dark (12:08:23.933), -" (12:08:23.943), -&gt; (12:08:23.953), -&lt; (12:08:23.963), -/ (12:08:23.973), -div (12:08:24.003), -&gt; (12:08:24.013), -&lt; (12:08:24.033), -div (12:08:24.063), -class (12:08:24.123), -= (12:08:24.133), -" (12:08:24.143), -cell (12:08:24.183), -light (12:08:24.243), -" (12:08:24.253), -&gt; (12:08:24.263), -&lt; (12:08:24.273), -/ (12:08:24.283), -div (12:08:24.313), -&gt; (12:08:24.323), -&lt; (12:08:24.343), -div (12:08:24.373), -class (12:08:24.433), -= (12:08:24.443), -" (12:08:24.453), -cell (12:08:24.493), -dark (12:08:24.543), -" (12:08:24.553), -&gt; (12:08:24.563), -&lt; (12:08:24.573), -/ (12:08:24.583), -div (12:08:24.613), -&gt; (12:08:24.623), -&lt; (12:08:24.643), -div (12:08:24.673), -class (12:08:24.733), -= (12:08:24.743), -" (12:08:24.753), -cell (12:08:24.793), -light (12:08:24.853), -dark (12:08:27.613), -" (12:08:27.623), -&gt; (12:08:27.633), -&lt; (12:08:27.643), -/ (12:08:27.653), -div (12:08:27.683), -&gt; (12:08:27.693), -&lt; (12:08:27.713), -div (12:08:27.743), -class (12:08:27.803), -= (12:08:27.813), -" (12:08:27.823), -cell (12:08:27.863), -" (12:08:28.233), -&gt; (12:08:28.243), -&lt; (12:08:28.253), -/ (12:08:28.263), -div (12:08:28.293), -&gt; (12:08:28.303), -&lt; (12:08:28.323), -div (12:08:28.353), -class (12:08:28.413), -= (12:08:28.423), -" (12:08:28.433), -cell (12:08:28.473), -light (12:08:28.533), -" (12:08:28.543), -&gt; (12:08:28.553), -&lt; (12:08:28.563), -/ (12:08:28.573), -div (12:08:28.603), -&gt; (12:08:28.613), -&lt; (12:08:28.633), -div (12:08:28.663), -class (12:08:28.723), -= (12:08:28.733), -" (12:08:28.743), -cell (12:08:28.783), -dark (12:08:28.833), -" (12:08:28.843), -&gt; (12:08:28.853), -&lt; (12:08:28.863), -/ (12:08:28.873), -div (12:08:28.903), -&gt; (12:08:28.913), -&lt; (12:08:28.933), -div (12:08:28.963), -class (12:08:29.023), -= (12:08:29.033), -" (12:08:29.043), -cell (12:08:29.083), -light (12:08:29.143), -" (12:08:29.153), -&gt; (12:08:29.163), -&lt; (12:08:29.173), -/ (12:08:29.183), -div (12:08:29.213), -&gt; (12:08:29.223), -&lt; (12:08:29.243), -div (12:08:29.273), -class (12:08:29.333), -= (12:08:29.343), -" (12:08:29.353), -cell (12:08:29.393), -dark (12:08:29.443), -" (12:08:29.453), -&gt; (12:08:29.463), -&lt; (12:08:29.473), -/ (12:08:29.483), -div (12:08:29.513), -&gt; (12:08:29.523), -&lt; (12:08:29.543), -div (12:08:29.573), -class (12:08:29.633), -= (12:08:29.643), -" (12:08:29.653), -cell (12:08:29.693), -light (12:08:29.753), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), +ing (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00), +} (00:00:00), +. (00:00:00), +invert (00:00:00), +- (00:00:00), +color (00:00:00), +{ (00:00:00), +filter (00:00:00), +: (00:00:00), +invert (00:00:00), +( (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-! (11:53:33.047), -&lt; (12:01:45.480), -/ (12:01:45.692), -style (12:01:46.591), -&gt; (12:01:46.854), -dark (12:08:22.713), -" (12:08:22.723), -&gt; (12:08:22.733), -&lt; (12:08:22.743), -/ (12:08:22.753), -div (12:08:22.783), -&gt; (12:08:22.793), -&lt; (12:08:22.813), -div (12:08:22.843), -class (12:08:22.903), -= (12:08:22.913), -" (12:08:22.923), -cell (12:08:22.963), -" (12:08:23.333), -&gt; (12:08:23.343), -&lt; (12:08:23.353), -/ (12:08:23.363), -div (12:08:23.393), -&gt; (12:08:23.403), -&lt; (12:08:23.423), -div (12:08:23.453), -class (12:08:23.513), -= (12:08:23.523), -" (12:08:23.533), -cell (12:08:23.573), -light (12:08:23.633), -" (12:08:23.643), -&gt; (12:08:23.653), -&lt; (12:08:23.663), -/ (12:08:23.673), -div (12:08:23.703), -&gt; (12:08:23.713), -&lt; (12:08:23.733), -div (12:08:23.763), -class (12:08:23.823), -= (12:08:23.833), -" (12:08:23.843), -cell (12:08:23.883), -dark (12:08:23.933), -" (12:08:23.943), -&gt; (12:08:23.953), -&lt; (12:08:23.963), -/ (12:08:23.973), -div (12:08:24.003), -&gt; (12:08:24.013), -&lt; (12:08:24.033), -div (12:08:24.063), -class (12:08:24.123), -= (12:08:24.133), -" (12:08:24.143), -cell (12:08:24.183), -light (12:08:24.243), -" (12:08:24.253), -&gt; (12:08:24.263), -&lt; (12:08:24.273), -/ (12:08:24.283), -div (12:08:24.313), -&gt; (12:08:24.323), -&lt; (12:08:24.343), -div (12:08:24.373), -class (12:08:24.433), -= (12:08:24.443), -" (12:08:24.453), -cell (12:08:24.493), -dark (12:08:24.543), -" (12:08:24.553), -&gt; (12:08:24.563), -&lt; (12:08:24.573), -/ (12:08:24.583), -div (12:08:24.613), -&gt; (12:08:24.623), -&lt; (12:08:24.643), -div (12:08:24.673), -class (12:08:24.733), -= (12:08:24.743), -" (12:08:24.753), -cell (12:08:24.793), -light (12:08:24.853), -dark (12:08:27.613), -" (12:08:27.623), -&gt; (12:08:27.633), -&lt; (12:08:27.643), -/ (12:08:27.653), -div (12:08:27.683), -&gt; (12:08:27.693), -&lt; (12:08:27.713), -div (12:08:27.743), -class (12:08:27.803), -= (12:08:27.813), -" (12:08:27.823), -cell (12:08:27.863), -" (12:08:28.233), -&gt; (12:08:28.243), -&lt; (12:08:28.253), -/ (12:08:28.263), -div (12:08:28.293), -&gt; (12:08:28.303), -&lt; (12:08:28.323), -div (12:08:28.353), -class (12:08:28.413), -= (12:08:28.423), -" (12:08:28.433), -cell (12:08:28.473), -light (12:08:28.533), -" (12:08:28.543), -&gt; (12:08:28.553), -&lt; (12:08:28.563), -/ (12:08:28.573), -div (12:08:28.603), -&gt; (12:08:28.613), -&lt; (12:08:28.633), -div (12:08:28.663), -class (12:08:28.723), -= (12:08:28.733), -" (12:08:28.743), -cell (12:08:28.783), -dark (12:08:28.833), -" (12:08:28.843), -&gt; (12:08:28.853), -&lt; (12:08:28.863), -/ (12:08:28.873), -div (12:08:28.903), -&gt; (12:08:28.913), -&lt; (12:08:28.933), -div (12:08:28.963), -class (12:08:29.023), -= (12:08:29.033), -" (12:08:29.043), -cell (12:08:29.083), -light (12:08:29.143), -" (12:08:29.153), -&gt; (12:08:29.163), -&lt; (12:08:29.173), -/ (12:08:29.183), -div (12:08:29.213), -&gt; (12:08:29.223), -&lt; (12:08:29.243), -div (12:08:29.273), -class (12:08:29.333), -= (12:08:29.343), -" (12:08:29.353), -cell (12:08:29.393), -dark (12:08:29.443), -" (12:08:29.453), -&gt; (12:08:29.463), -&lt; (12:08:29.473), -/ (12:08:29.483), -div (12:08:29.513), -&gt; (12:08:29.523), -&lt; (12:08:29.543), -div (12:08:29.573), -class (12:08:29.633), -= (12:08:29.643), -" (12:08:29.653), -cell (12:08:29.693), -light (12:08:29.753), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563) ~1.00, -class (12:08:33.623) ~1.00, -= (12:08:33.633) ~1.00, -" (12:08:33.643) ~1.00, -cell (12:08:33.683) ~1.00, -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053) ~1.00, -&gt; (12:08:34.063) ~1.00, -&lt; (12:08:34.073) ~1.00, -/ (12:08:34.083) ~1.00, -div (12:08:34.113) ~1.00, -&gt; (12:08:34.123) ~1.00, -&lt; (12:08:34.143) ~1.00, -div (12:08:34.173) ~1.00, -class (12:08:34.233) ~1.00, -= (12:08:34.243) ~1.00, -" (12:08:34.253) ~1.00, -cell (12:08:34.293) ~1.00, -dark (12:08:34.343) ~1.00, -" (12:08:34.353) ~1.00, -&gt; (12:08:34.363) ~1.00, -&lt; (12:08:34.373) ~1.00, -/ (12:08:34.383) ~1.00, -div (12:08:34.413) ~1.00, -&gt; (12:08:34.423) ~1.00, -&lt; (12:08:34.443) ~1.00, -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653) ~1.00, +ing (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00), +} (00:00:00), +. (00:00:00), +invert (00:00:00), +- (00:00:00), +color (00:00:00), +{ (00:00:00), +filter (00:00:00), +: (00:00:00), +invert (00:00:00), +( (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="O59" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>-} (12:02:03.928), -; (12:02:47.484), -; (12:02:56.888), -img (12:17:42.332), -{ (12:17:43.944), -} (12:17:44.771), -width (12:17:46.547), -: (12:17:46.642), +;* (12:18:30.043), -50 (12:20:14.705), -% (12:20:15.067), -; (12:20:15.756), -flex (12:24:01.038), -; (12:24:01.089), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), +} (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +; (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +/ (00:00:00), +anonymous (00:00:00), +function (00:00:00), +handleclick (00:00:00), +( (00:00:00), +cell (00:00:00), +) (00:00:00), +console (00:00:00), +. (00:00:00), +long (00:00:00), +element (00:00:00), +; (00:00:00)</t>
+          <t>-} (12:02:03.928), -; (12:02:47.484), -; (12:02:56.888), -img (12:17:42.332) ~0.67, -{ (12:17:43.944) ~1.00, -} (12:17:44.771) ~1.00, -width (12:17:46.547) ~1.00, -: (12:17:46.642) ~1.00, +;* (12:18:30.043), -50 (12:20:14.705) ~1.00, -% (12:20:15.067) ~1.00, -; (12:20:15.756), -flex (12:24:01.038), -; (12:24:01.089) ~1.00, -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -. (12:26:59.213) ~1.00, -invert (12:27:00.293) ~1.00, -- (12:27:00.514) ~1.00, -color (12:27:01.097) ~1.00, -{ (12:27:01.630) ~1.00, -} (12:27:01.824) ~1.00, -filter (12:27:03.521) ~1.00, -: (12:27:03.624) ~1.00, -invert (12:27:04.621) ~1.00, -( (12:27:04.730) ~1.00, -100 (12:27:05.245) ~1.00, -% (12:27:05.347) ~1.00, -) (12:27:05.426) ~1.00, -; (12:27:05.639) ~1.00, +} (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +; (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +/ (00:00:00), +anonymous (00:00:00), +function (00:00:00), +handleclick (00:00:00), +( (00:00:00), +cell (00:00:00), +) (00:00:00), +console (00:00:00), +. (00:00:00), +long (00:00:00), +element (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>-} (12:33:32.526), -for (12:45:10.759), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -{ (12:45:13.433), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102)</t>
+          <t>-} (12:33:32.526), -for (12:45:10.759) ~0.25, -const (12:45:11.606) ~0.57, -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133) ~0.14, -{ (12:45:13.433) ~0.00, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102)</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>-DOCTYPE (11:53:34.288), -&gt; (11:58:37.856), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +DOCTYOE (00:00:00)</t>
+          <t>-DOCTYPE (11:53:34.288) ~0.86, -&gt; (11:58:37.856), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +DOCTYOE (00:00:00)</t>
         </is>
       </c>
       <c r="O66" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>-} (12:33:32.526), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -selectedPiece (12:52:11.048), +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00)</t>
+          <t>-} (12:33:32.526), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -selectedPiece (12:52:11.048) ~0.92, +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00)</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>-&lt; (11:53:50.287), -/ (11:53:50.722), -html (11:53:51.658), -&gt; (11:53:52.247), -&lt; (11:54:54.301), -/ (11:54:54.552), -body (11:54:55.321), -&gt; (11:54:55.640), -/ (11:58:31.581), -dark (11:58:37.525), -/ (12:25:38.278), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), +"* (12:49:43.795), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Game (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +black (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +cell (00:00:00), +dark (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00)</t>
+          <t>-&lt; (11:53:50.287), -/ (11:53:50.722), -html (11:53:51.658), -&gt; (11:53:52.247), -&lt; (11:54:54.301), -/ (11:54:54.552), -body (11:54:55.321), -&gt; (11:54:55.640), -/ (11:58:31.581) ~1.00, -dark (11:58:37.525) ~1.00, -/ (12:25:38.278) ~1.00, -invert (12:26:41.264) ~0.17, -- (12:26:41.305) ~0.00, -color (12:26:42.154) ~0.40, +"* (12:49:43.795), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Game (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +black (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +cell (00:00:00), +dark (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00)</t>
         </is>
       </c>
       <c r="O68" t="n">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>-} (12:02:52.276), -gray (12:02:56.667), -; (12:02:56.888), -# (12:03:33.003), -chess (12:03:34.679), -- (12:03:34.891), -board (12:03:35.921), -{ (12:03:45.639), -width (12:03:53.681), -: (12:03:53.818), -400px (12:03:55.740), -; (12:03:56.458), -height (12:03:58.438), -: (12:03:58.649), -400px (12:03:59.637), -; (12:03:59.993), -display (12:04:30.837), -: (12:04:30.966), -grid (12:04:31.833), -; (12:04:31.971), -grid (12:04:33.784), -- (12:04:33.928), -template (12:04:35.620), -- (12:04:35.828), -rows (12:04:36.631), -: (12:04:36.826), -repeat (12:04:38.281), -( (12:04:38.485), -8 (12:04:38.643), -, (12:04:38.821), -1fr (12:04:39.902), -) (12:04:40.295), -; (12:04:41.132), -grid (12:05:13.862), -- (12:05:13.980), -template (12:05:15.274), -- (12:05:15.459), -columns (12:05:17.007), -: (12:05:17.574), -repeat (12:05:19.260), -( (12:05:19.386), -8 (12:05:19.565), -, (12:05:19.720), -1fr (12:05:20.402), -) (12:05:20.749), -} (12:17:44.771), -50 (12:20:14.705), -; (12:20:15.756), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +400px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +400px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +grid (00:00:00), +; (00:00:00), +grid (00:00:00), +- (00:00:00), +template (00:00:00), +- (00:00:00), +columns (00:00:00), +: (00:00:00), +repeat (00:00:00), +( (00:00:00), +8 (00:00:00), +, (00:00:00), +1fr (00:00:00), +) (00:00:00), +; (00:00:00), +grid (00:00:00), +- (00:00:00), +template (00:00:00), +- (00:00:00), +rows (00:00:00), +: (00:00:00), +repeat (00:00:00), +( (00:00:00), +8 (00:00:00), +, (00:00:00), +1fr (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +grey (00:00:00), +60 (00:00:00)</t>
+          <t>-} (12:02:52.276), -gray (12:02:56.667) ~0.75, -; (12:02:56.888), -# (12:03:33.003) ~1.00, -chess (12:03:34.679) ~1.00, -- (12:03:34.891) ~1.00, -board (12:03:35.921) ~1.00, -{ (12:03:45.639) ~1.00, -width (12:03:53.681) ~1.00, -: (12:03:53.818) ~1.00, -400px (12:03:55.740) ~1.00, -; (12:03:56.458) ~1.00, -height (12:03:58.438) ~1.00, -: (12:03:58.649) ~1.00, -400px (12:03:59.637) ~1.00, -; (12:03:59.993) ~1.00, -display (12:04:30.837) ~1.00, -: (12:04:30.966) ~1.00, -grid (12:04:31.833) ~1.00, -; (12:04:31.971) ~1.00, -grid (12:04:33.784) ~1.00, -- (12:04:33.928) ~1.00, -template (12:04:35.620) ~1.00, -- (12:04:35.828) ~1.00, -rows (12:04:36.631) ~0.29, -: (12:04:36.826) ~1.00, -repeat (12:04:38.281) ~1.00, -( (12:04:38.485) ~1.00, -8 (12:04:38.643) ~1.00, -, (12:04:38.821) ~1.00, -1fr (12:04:39.902) ~1.00, -) (12:04:40.295) ~1.00, -; (12:04:41.132) ~1.00, -grid (12:05:13.862) ~1.00, -- (12:05:13.980) ~1.00, -template (12:05:15.274) ~1.00, -- (12:05:15.459) ~1.00, -columns (12:05:17.007) ~0.29, -: (12:05:17.574) ~1.00, -repeat (12:05:19.260) ~1.00, -( (12:05:19.386) ~1.00, -8 (12:05:19.565) ~1.00, -, (12:05:19.720) ~1.00, -1fr (12:05:20.402) ~1.00, -) (12:05:20.749) ~1.00, -} (12:17:44.771), -50 (12:20:14.705), -; (12:20:15.756), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245) ~0.33, -% (12:27:05.347), -) (12:27:05.426), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +400px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +400px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +grid (00:00:00), +; (00:00:00), +grid (00:00:00), +- (00:00:00), +template (00:00:00), +- (00:00:00), +columns (00:00:00), +: (00:00:00), +repeat (00:00:00), +( (00:00:00), +8 (00:00:00), +, (00:00:00), +1fr (00:00:00), +) (00:00:00), +; (00:00:00), +grid (00:00:00), +- (00:00:00), +template (00:00:00), +- (00:00:00), +rows (00:00:00), +: (00:00:00), +repeat (00:00:00), +( (00:00:00), +8 (00:00:00), +, (00:00:00), +1fr (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +grey (00:00:00), +60 (00:00:00)</t>
         </is>
       </c>
       <c r="Q68" t="n">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>-cells (12:37:50.791), -getElementsByClassName (12:37:56.278), -cell (12:41:05.940), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), -let (12:56:53.102), +board (00:00:00), +getElementById (00:00:00), +this (00:00:00), +selectedpice (00:00:00), += (00:00:00), +replaceChild (00:00:00), +selectedpice (00:00:00), +selectedpice (00:00:00), +selectedpiece (00:00:00), +return (00:00:00), +; (00:00:00)</t>
+          <t>-cells (12:37:50.791), -getElementsByClassName (12:37:56.278) ~0.55, -cell (12:41:05.940) ~0.00, -selectedPiece (12:51:24.571) ~0.08, -= (12:51:25.051) ~1.00, -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:52:11.048) ~0.85, -replaceChildren (12:52:19.891) ~0.80, -selectedPiece (12:52:27.102) ~0.85, -selectedPiece (12:52:30.641) ~0.85, -selectedPiece (12:53:29.626) ~0.92, -let (12:56:53.102), +board (00:00:00), +getElementById (00:00:00), +this (00:00:00), +selectedpice (00:00:00), += (00:00:00), +replaceChild (00:00:00), +selectedpice (00:00:00), +selectedpice (00:00:00), +selectedpiece (00:00:00), +return (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>-Chess (11:54:35.668), -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -&gt; (12:25:38.438), -" (12:26:40.406), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +" (00:00:00), +' (00:00:00)</t>
+          <t>-Chess (11:54:35.668) ~0.80, -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953) ~1.00, -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -&gt; (12:25:38.438), -" (12:26:40.406) ~0.00, +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +" (00:00:00), +' (00:00:00)</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>-; (12:02:47.484), -; (12:02:56.888), -columns (12:05:17.007), -} (12:17:44.771), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -) (12:27:05.426), +: (00:00:00), +: (00:00:00), +/ (00:00:00), +1 (00:00:00), +fraction (00:00:00), +/ (00:00:00), +coloumns (00:00:00), +height (00:00:00), +50 (00:00:00)</t>
+          <t>-; (12:02:47.484) ~0.00, -; (12:02:56.888) ~0.00, -columns (12:05:17.007) ~0.88, -} (12:17:44.771), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245) ~0.33, -) (12:27:05.426), +: (00:00:00), +: (00:00:00), +/ (00:00:00), +1 (00:00:00), +fraction (00:00:00), +/ (00:00:00), +coloumns (00:00:00), +height (00:00:00), +50 (00:00:00)</t>
         </is>
       </c>
       <c r="Q70" t="n">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>-getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00), +selectedpiece (00:00:00), +replaceChirldren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00)</t>
+          <t>-getElementsByClassName (12:37:56.278) ~0.50, -onclick (12:41:03.120) ~0.86, -selectedPiece (12:51:24.571) ~0.92, -selectedPiece (12:52:11.048) ~0.92, -replaceChildren (12:52:19.891) ~0.94, -selectedPiece (12:52:27.102) ~0.92, -selectedPiece (12:52:30.641) ~0.92, -selectedPiece (12:53:29.626) ~0.92, +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00), +selectedpiece (00:00:00), +replaceChirldren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00)</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>-gray (12:02:56.667), -; (12:05:21.226), +grey (00:00:00)</t>
+          <t>-gray (12:02:56.667) ~0.75, -; (12:05:21.226), +grey (00:00:00)</t>
         </is>
       </c>
       <c r="Q71" t="n">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>-dark (11:58:37.525), -pieces (12:16:05.490), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Pieces (00:00:00), +light (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +cell (00:00:00), +dark (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +anonymous (00:00:00), +function (00:00:00), +Children (00:00:00)</t>
+          <t>-dark (11:58:37.525) ~1.00, -pieces (12:16:05.490) ~0.83, -img (12:25:35.614) ~0.20, -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154) ~0.40, +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +Pieces (00:00:00), +light (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +cell (00:00:00), +dark (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +anonymous (00:00:00), +function (00:00:00), +Children (00:00:00)</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>-} (12:33:32.526), -children (12:53:24.251)</t>
+          <t>-} (12:33:32.526), -children (12:53:24.251) ~0.88</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>-&lt; (11:53:50.287), -/ (11:53:50.722), -html (11:53:51.658), -&gt; (11:53:52.247), -&lt; (11:54:54.301), -/ (11:54:54.552), -body (11:54:55.321), -&gt; (11:54:55.640), -/ (12:16:05.559), -/ (12:25:37.107), -&lt; (12:32:56.391), -/ (12:32:56.665), -script (12:32:57.709), -&gt; (12:32:57.900), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +handleclick (00:00:00), +\ (00:00:00), +\ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00)</t>
+          <t>-&lt; (11:53:50.287), -/ (11:53:50.722), -html (11:53:51.658), -&gt; (11:53:52.247), -&lt; (11:54:54.301), -/ (11:54:54.552), -body (11:54:55.321), -&gt; (11:54:55.640), -/ (12:16:05.559) ~0.00, -/ (12:25:37.107) ~0.00, -&lt; (12:32:56.391), -/ (12:32:56.665), -script (12:32:57.709), -&gt; (12:32:57.900), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +handleclick (00:00:00), +\ (00:00:00), +\ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00)</t>
         </is>
       </c>
       <c r="O73" t="n">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>-element (12:33:31.280), -} (12:33:32.526), -element (12:35:29.854), -. (12:35:29.918), -style (12:35:30.684), -. (12:35:30.708), -border (12:35:31.651), -= (12:35:31.979), -" (12:35:32.153), -4px (12:35:32.780), -solid (12:35:33.773), -red (12:35:34.503), -" (12:35:34.724), -; (12:35:34.812), -handleClick (12:41:05.134), -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +handClick (00:00:00), +eleement (00:00:00), +00 (00:00:00)</t>
+          <t>-element (12:33:31.280) ~0.88, -} (12:33:32.526), -element (12:35:29.854), -. (12:35:29.918), -style (12:35:30.684), -. (12:35:30.708), -border (12:35:31.651), -= (12:35:31.979), -" (12:35:32.153), -4px (12:35:32.780), -solid (12:35:33.773), -red (12:35:34.503), -" (12:35:34.724), -; (12:35:34.812), -handleClick (12:41:05.134) ~0.82, -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +handClick (00:00:00), +eleement (00:00:00), +00 (00:00:00)</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>-DOCTYPE (11:53:34.288), -123456 (11:54:38.411), -&gt; (11:58:37.856), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), -&lt; (12:32:56.391), -/ (12:32:56.665), -script (12:32:57.709), -&gt; (12:32:57.900), +DOCTYOE (00:00:00), +654321 (00:00:00)</t>
+          <t>-DOCTYPE (11:53:34.288) ~0.86, -123456 (11:54:38.411) ~0.00, -&gt; (11:58:37.856), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), -&lt; (12:32:56.391), -/ (12:32:56.665), -script (12:32:57.709), -&gt; (12:32:57.900), +DOCTYOE (00:00:00), +654321 (00:00:00)</t>
         </is>
       </c>
       <c r="O75" t="n">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>-} (12:33:32.526), -getElementsByClassName (12:37:56.278), -handleClick (12:41:05.134), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -} (12:45:14.115), -cell (12:45:15.612), -style (12:45:16.268), -. (12:45:16.371), -border (12:45:17.066), -= (12:45:17.426), -" (12:45:17.580), -" (12:45:17.718), -; (12:45:17.816), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -let (12:56:53.102), +getElementsbyClassName (00:00:00), +handleclick (00:00:00), +console (00:00:00), +log (00:00:00)</t>
+          <t>-} (12:33:32.526), -getElementsByClassName (12:37:56.278) ~0.95, -handleClick (12:41:05.134), -; (12:41:06.130), -function (12:42:53.629) ~0.27, -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606) ~0.57, -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -} (12:45:14.115), -cell (12:45:15.612), -style (12:45:16.268), -. (12:45:16.371), -border (12:45:17.066), -= (12:45:17.426), -" (12:45:17.580), -" (12:45:17.718), -; (12:45:17.816), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -let (12:56:53.102), +getElementsbyClassName (00:00:00), +handleclick (00:00:00), +console (00:00:00), +log (00:00:00)</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>-Chess (11:54:35.668), -Chess (11:56:36.040), -Game (11:56:37.110), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +chess (00:00:00), +game (00:00:00), +" (00:00:00), +handleclick (00:00:00)</t>
+          <t>-Chess (11:54:35.668) ~0.80, -Chess (11:56:36.040) ~0.80, -Game (11:56:37.110) ~0.75, +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +chess (00:00:00), +game (00:00:00), +" (00:00:00), +handleclick (00:00:00)</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>-handleClick (12:33:15.189), -handleClick (12:41:05.134), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), +selectedpiece (00:00:00), +handleclick (00:00:00), +handleclick (00:00:00), +selectedpiece (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00)</t>
+          <t>-handleClick (12:33:15.189) ~0.91, -handleClick (12:41:05.134) ~0.91, -selectedPiece (12:51:24.571) ~0.92, -selectedPiece (12:52:11.048) ~0.92, -replaceChildren (12:52:19.891) ~0.93, -selectedPiece (12:52:27.102) ~0.92, -selectedPiece (12:52:30.641) ~0.92, -selectedPiece (12:53:29.626) ~0.92, +selectedpiece (00:00:00), +handleclick (00:00:00), +handleclick (00:00:00), +selectedpiece (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00)</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>-/ (12:16:06.943), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p6 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p4 (00:00:00), +. (00:00:00), +png (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p3 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p6 (00:00:00), +. (00:00:00), +png (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p5 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p2 (00:00:00), +. (00:00:00), +png (00:00:00)</t>
+          <t>-/ (12:16:06.943) ~1.00, +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +handleClick* (12:49:47.595), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p6 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p4 (00:00:00), +. (00:00:00), +png (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p3 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p6 (00:00:00), +. (00:00:00), +png (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p5 (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +pieces (00:00:00), +/ (00:00:00), +p2 (00:00:00), +. (00:00:00), +png (00:00:00)</t>
         </is>
       </c>
       <c r="O82" t="n">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>-} (12:03:46.236), -; (12:05:21.226), -img (12:17:42.332), -{ (12:17:43.944), -width (12:17:46.547), -: (12:17:46.642), -50 (12:20:14.705), -% (12:20:15.067), -; (12:20:15.756), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +; (00:00:00), +} (00:00:00), +img (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00)</t>
+          <t>-} (12:03:46.236) ~1.00, -; (12:05:21.226) ~1.00, -img (12:17:42.332) ~1.00, -{ (12:17:43.944) ~1.00, -width (12:17:46.547) ~1.00, -: (12:17:46.642), -50 (12:20:14.705) ~1.00, -% (12:20:15.067) ~1.00, -; (12:20:15.756), -: (12:24:02.925) ~1.00, -center (12:24:03.906) ~1.00, -; (12:24:04.138) ~1.00, -justify (12:24:05.215) ~1.00, -- (12:24:05.313) ~1.00, -content (12:24:06.156) ~1.00, +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +; (00:00:00), +} (00:00:00), +img (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00)</t>
         </is>
       </c>
       <c r="Q82" t="n">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>-Chess (11:54:35.668), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +" (00:00:00), +handelClick (00:00:00)</t>
+          <t>-Chess (11:54:35.668) ~0.80, +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +chess (00:00:00), +" (00:00:00), +handelClick (00:00:00)</t>
         </is>
       </c>
       <c r="O83" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>-handleClick (12:33:15.189), +const* (12:56:52.436), -let (12:56:53.102), +handelClick (00:00:00)</t>
+          <t>-handleClick (12:33:15.189) ~0.82, +const* (12:56:52.436), -let (12:56:53.102), +handelClick (00:00:00)</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
